--- a/outputs/tables/tabla_09_costo_capital.xlsx
+++ b/outputs/tables/tabla_09_costo_capital.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="costo_capital" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,82 +444,87 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>grado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_importado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ratio_costo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>ingreso_cop</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>costo_total_cop</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>costo_importado_cop</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>margen_cop</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>margen_pct</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>margen_pct_min</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>margen_pct_max</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>margen_pct_factor_060</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>costo_financiero_30d</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>margen_neto_30d</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>margen_neto_pct_30d</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>margen_neto_30d_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>costo_financiero_60d</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>margen_neto_60d</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>margen_neto_pct_60d</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>margen_neto_60d_pct</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>costo_financiero_90d</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>margen_neto_90d</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>margen_neto_pct_90d</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>dias_breakeven_capital</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>costo_financiero_90d_ibr_max</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>margen_neto_90d_ibr_max</t>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>margen_neto_90d_pct</t>
         </is>
       </c>
     </row>
@@ -541,59 +546,64 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F2" t="n">
-        <v>13174.81311303553</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>8135.412926987981</v>
+        <v>0.25</v>
       </c>
       <c r="H2" t="n">
-        <v>5039.400186047544</v>
+        <v>0.62</v>
       </c>
       <c r="I2" t="n">
-        <v>38.25025936088172</v>
+        <v>24474.98275334492</v>
       </c>
       <c r="J2" t="n">
-        <v>74.7967635627021</v>
+        <v>17968.8752352061</v>
       </c>
       <c r="K2" t="n">
-        <v>4964.603422484842</v>
+        <v>3768.492081185129</v>
       </c>
       <c r="L2" t="n">
-        <v>37.68253393721939</v>
+        <v>6506.107518138819</v>
       </c>
       <c r="M2" t="n">
-        <v>149.5935271254042</v>
+        <v>26.58268479167631</v>
       </c>
       <c r="N2" t="n">
-        <v>4889.80665892214</v>
+        <v>15.72924688168051</v>
       </c>
       <c r="O2" t="n">
-        <v>37.11480851355705</v>
+        <v>39.60681028367127</v>
       </c>
       <c r="P2" t="n">
-        <v>224.3902906881063</v>
+        <v>28.75337237367547</v>
       </c>
       <c r="Q2" t="n">
-        <v>4815.009895359437</v>
+        <v>261.1462198479249</v>
       </c>
       <c r="R2" t="n">
-        <v>36.54708308989471</v>
+        <v>25.51569233460406</v>
       </c>
       <c r="S2" t="n">
-        <v>2021.237261886211</v>
+        <v>526.0877439231984</v>
       </c>
       <c r="T2" t="n">
-        <v>246.7169841921169</v>
+        <v>24.43319300561448</v>
       </c>
       <c r="U2" t="n">
-        <v>4792.683201855427</v>
+        <v>794.8797303444612</v>
+      </c>
+      <c r="V2" t="n">
+        <v>23.33496143940621</v>
       </c>
     </row>
     <row r="3">
@@ -614,59 +624,64 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F3" t="n">
-        <v>14492.29442433908</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>8135.412926987981</v>
+        <v>0.25</v>
       </c>
       <c r="H3" t="n">
-        <v>6356.8814973511</v>
+        <v>0.62</v>
       </c>
       <c r="I3" t="n">
-        <v>43.86387214625613</v>
+        <v>27476.20732599355</v>
       </c>
       <c r="J3" t="n">
-        <v>74.7967635627021</v>
+        <v>18599.13239546231</v>
       </c>
       <c r="K3" t="n">
-        <v>6282.084733788398</v>
+        <v>4233.681889945667</v>
       </c>
       <c r="L3" t="n">
-        <v>43.34775812474491</v>
+        <v>8877.074930531235</v>
       </c>
       <c r="M3" t="n">
-        <v>149.5935271254042</v>
+        <v>32.30822516808272</v>
       </c>
       <c r="N3" t="n">
-        <v>6207.287970225696</v>
+        <v>22.36723280867265</v>
       </c>
       <c r="O3" t="n">
-        <v>42.83164410323369</v>
+        <v>44.2374159993748</v>
       </c>
       <c r="P3" t="n">
-        <v>224.3902906881063</v>
+        <v>34.29642363996474</v>
       </c>
       <c r="Q3" t="n">
-        <v>6132.491206662993</v>
+        <v>270.3059069612574</v>
       </c>
       <c r="R3" t="n">
-        <v>42.31553008172247</v>
+        <v>31.32444344102632</v>
       </c>
       <c r="S3" t="n">
-        <v>2549.661721134014</v>
+        <v>544.540238205144</v>
       </c>
       <c r="T3" t="n">
-        <v>246.7169841921169</v>
+        <v>30.3263641646902</v>
       </c>
       <c r="U3" t="n">
-        <v>6110.164513158983</v>
+        <v>822.7600865178163</v>
+      </c>
+      <c r="V3" t="n">
+        <v>29.31377954916553</v>
       </c>
     </row>
     <row r="4">
@@ -687,59 +702,64 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11198.5911460802</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>8135.412926987981</v>
+        <v>0.25</v>
       </c>
       <c r="H4" t="n">
-        <v>3063.178219092215</v>
+        <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>27.35324630691968</v>
+        <v>31198.94614995836</v>
       </c>
       <c r="J4" t="n">
-        <v>74.7967635627021</v>
+        <v>19380.90754849492</v>
       </c>
       <c r="K4" t="n">
-        <v>2988.381455529513</v>
+        <v>4810.706407660213</v>
       </c>
       <c r="L4" t="n">
-        <v>26.68533404378751</v>
+        <v>11818.03860146344</v>
       </c>
       <c r="M4" t="n">
-        <v>149.5935271254042</v>
+        <v>37.8796083196522</v>
       </c>
       <c r="N4" t="n">
-        <v>2913.584691966811</v>
+        <v>28.8264943844702</v>
       </c>
       <c r="O4" t="n">
-        <v>26.01742178065535</v>
+        <v>48.7433450418706</v>
       </c>
       <c r="P4" t="n">
-        <v>224.3902906881063</v>
+        <v>39.69023110668861</v>
       </c>
       <c r="Q4" t="n">
-        <v>2838.787928404109</v>
+        <v>281.6676434813874</v>
       </c>
       <c r="R4" t="n">
-        <v>25.34950951752319</v>
+        <v>36.97679691657612</v>
       </c>
       <c r="S4" t="n">
-        <v>1228.600573014508</v>
+        <v>567.4288342430486</v>
       </c>
       <c r="T4" t="n">
-        <v>246.7169841921169</v>
+        <v>36.06086472646898</v>
       </c>
       <c r="U4" t="n">
-        <v>2816.461234900098</v>
+        <v>857.3430648455321</v>
+      </c>
+      <c r="V4" t="n">
+        <v>35.13162106160605</v>
       </c>
     </row>
     <row r="5">
@@ -760,59 +780,64 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13174.81311303553</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G5" t="n">
-        <v>9069.123925321315</v>
+        <v>0.25</v>
       </c>
       <c r="H5" t="n">
-        <v>4105.68918771421</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>31.16316833103255</v>
+        <v>25131.67118667825</v>
       </c>
       <c r="J5" t="n">
-        <v>83.38127690025553</v>
+        <v>18625.56366853943</v>
       </c>
       <c r="K5" t="n">
-        <v>4022.307910813954</v>
+        <v>3768.492081185129</v>
       </c>
       <c r="L5" t="n">
-        <v>30.53028438660865</v>
+        <v>6506.107518138819</v>
       </c>
       <c r="M5" t="n">
-        <v>166.7625538005111</v>
+        <v>25.88808149609869</v>
       </c>
       <c r="N5" t="n">
-        <v>3938.926633913699</v>
+        <v>15.318242996761</v>
       </c>
       <c r="O5" t="n">
-        <v>29.89740044218476</v>
+        <v>38.57188769530391</v>
       </c>
       <c r="P5" t="n">
-        <v>250.1438307007666</v>
+        <v>28.00204919596623</v>
       </c>
       <c r="Q5" t="n">
-        <v>3855.545357013443</v>
+        <v>270.6900393546047</v>
       </c>
       <c r="R5" t="n">
-        <v>29.26451649776087</v>
+        <v>24.81099419321335</v>
       </c>
       <c r="S5" t="n">
-        <v>1477.198241743991</v>
+        <v>545.3140856853088</v>
       </c>
       <c r="T5" t="n">
-        <v>275.0329853199292</v>
+        <v>23.71825330745691</v>
       </c>
       <c r="U5" t="n">
-        <v>3830.656202394281</v>
+        <v>823.9293129129686</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.60963134134052</v>
       </c>
     </row>
     <row r="6">
@@ -833,59 +858,64 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14492.29442433908</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G6" t="n">
-        <v>9069.123925321315</v>
+        <v>0.25</v>
       </c>
       <c r="H6" t="n">
-        <v>5423.170499017766</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>37.42106211912051</v>
+        <v>28132.89575932688</v>
       </c>
       <c r="J6" t="n">
-        <v>83.38127690025553</v>
+        <v>19255.82082879564</v>
       </c>
       <c r="K6" t="n">
-        <v>5339.789222117511</v>
+        <v>4233.681889945667</v>
       </c>
       <c r="L6" t="n">
-        <v>36.84571307873515</v>
+        <v>8877.074930531235</v>
       </c>
       <c r="M6" t="n">
-        <v>166.7625538005111</v>
+        <v>31.55407465507075</v>
       </c>
       <c r="N6" t="n">
-        <v>5256.407945217255</v>
+        <v>21.84512860735666</v>
       </c>
       <c r="O6" t="n">
-        <v>36.2703640383498</v>
+        <v>43.20480991232763</v>
       </c>
       <c r="P6" t="n">
-        <v>250.1438307007666</v>
+        <v>33.49586386461355</v>
       </c>
       <c r="Q6" t="n">
-        <v>5173.026668316999</v>
+        <v>279.8497264679373</v>
       </c>
       <c r="R6" t="n">
-        <v>35.69501499796444</v>
+        <v>30.55933266739193</v>
       </c>
       <c r="S6" t="n">
-        <v>1951.218798977572</v>
+        <v>563.7665799672543</v>
       </c>
       <c r="T6" t="n">
-        <v>275.0329853199292</v>
+        <v>29.55013384218678</v>
       </c>
       <c r="U6" t="n">
-        <v>5148.137513697837</v>
+        <v>851.8096690863235</v>
+      </c>
+      <c r="V6" t="n">
+        <v>28.52626807456997</v>
       </c>
     </row>
     <row r="7">
@@ -906,59 +936,64 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F7" t="n">
-        <v>11198.5911460802</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G7" t="n">
-        <v>9069.123925321315</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>2129.467220758881</v>
+        <v>0.62</v>
       </c>
       <c r="I7" t="n">
-        <v>19.01549215415594</v>
+        <v>31855.63458329169</v>
       </c>
       <c r="J7" t="n">
-        <v>83.38127690025553</v>
+        <v>20037.59598182826</v>
       </c>
       <c r="K7" t="n">
-        <v>2046.085943858626</v>
+        <v>4810.706407660213</v>
       </c>
       <c r="L7" t="n">
-        <v>18.27092280777489</v>
+        <v>11818.03860146344</v>
       </c>
       <c r="M7" t="n">
-        <v>166.7625538005111</v>
+        <v>37.09873859383735</v>
       </c>
       <c r="N7" t="n">
-        <v>1962.70466695837</v>
+        <v>28.23225020495671</v>
       </c>
       <c r="O7" t="n">
-        <v>17.52635346139384</v>
+        <v>47.73852466049415</v>
       </c>
       <c r="P7" t="n">
-        <v>250.1438307007666</v>
+        <v>38.87203627161349</v>
       </c>
       <c r="Q7" t="n">
-        <v>1879.323390058114</v>
+        <v>291.2114629880672</v>
       </c>
       <c r="R7" t="n">
-        <v>16.78178411501278</v>
+        <v>36.18457861304448</v>
       </c>
       <c r="S7" t="n">
-        <v>766.1674058936204</v>
+        <v>586.655176005159</v>
       </c>
       <c r="T7" t="n">
-        <v>275.0329853199292</v>
+        <v>35.25713291346312</v>
       </c>
       <c r="U7" t="n">
-        <v>1854.434235438952</v>
+        <v>886.3926474140395</v>
+      </c>
+      <c r="V7" t="n">
+        <v>34.31620841037351</v>
       </c>
     </row>
     <row r="8">
@@ -979,59 +1014,64 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F8" t="n">
-        <v>362.307360608477</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G8" t="n">
-        <v>447.9094755317528</v>
+        <v>0.15</v>
       </c>
       <c r="H8" t="n">
-        <v>-85.60211492327585</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>-23.62693233157378</v>
+        <v>320.2173139347174</v>
       </c>
       <c r="J8" t="n">
-        <v>4.118067446546455</v>
+        <v>318.626219456832</v>
       </c>
       <c r="K8" t="n">
-        <v>-89.72018236982231</v>
+        <v>34.89704502667647</v>
       </c>
       <c r="L8" t="n">
-        <v>-24.76355496039103</v>
+        <v>1.591094477885406</v>
       </c>
       <c r="M8" t="n">
-        <v>8.23613489309291</v>
+        <v>0.4968795904052152</v>
       </c>
       <c r="N8" t="n">
-        <v>-93.83824981636876</v>
+        <v>-8.94735354547915</v>
       </c>
       <c r="O8" t="n">
-        <v>-25.90017758920827</v>
+        <v>14.66322929423178</v>
       </c>
       <c r="P8" t="n">
-        <v>12.35420233963936</v>
+        <v>24.10746243011616</v>
       </c>
       <c r="Q8" t="n">
-        <v>-97.95631726291521</v>
+        <v>4.630675635866122</v>
       </c>
       <c r="R8" t="n">
-        <v>-27.03680021802552</v>
+        <v>-0.9492244877803186</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>9.328650054868058</v>
       </c>
       <c r="T8" t="n">
-        <v>13.58343774139322</v>
+        <v>-2.416345163197549</v>
       </c>
       <c r="U8" t="n">
-        <v>-99.18555266466907</v>
+        <v>14.09490132728482</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-3.904787875382828</v>
       </c>
     </row>
     <row r="9">
@@ -1052,59 +1092,64 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F9" t="n">
-        <v>398.5380966693247</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G9" t="n">
-        <v>447.9094755317528</v>
+        <v>0.15</v>
       </c>
       <c r="H9" t="n">
-        <v>-49.37137886242812</v>
+        <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-12.3881203014307</v>
+        <v>354.0036465934201</v>
       </c>
       <c r="J9" t="n">
-        <v>4.118067446546455</v>
+        <v>324.7922251670452</v>
       </c>
       <c r="K9" t="n">
-        <v>-53.48944630897457</v>
+        <v>39.20480244066107</v>
       </c>
       <c r="L9" t="n">
-        <v>-13.42141360035547</v>
+        <v>29.2114214263749</v>
       </c>
       <c r="M9" t="n">
-        <v>8.23613489309291</v>
+        <v>8.251728960273894</v>
       </c>
       <c r="N9" t="n">
-        <v>-57.60751375552103</v>
+        <v>-0.4343015242249316</v>
       </c>
       <c r="O9" t="n">
-        <v>-14.45470689928024</v>
+        <v>21.28077468702217</v>
       </c>
       <c r="P9" t="n">
-        <v>12.35420233963936</v>
+        <v>29.966805171521</v>
       </c>
       <c r="Q9" t="n">
-        <v>-61.72558120206748</v>
+        <v>4.720287760259307</v>
       </c>
       <c r="R9" t="n">
-        <v>-15.48800019820501</v>
+        <v>6.918328074242727</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9.509176659379619</v>
       </c>
       <c r="T9" t="n">
-        <v>13.58343774139322</v>
+        <v>5.565548535047629</v>
       </c>
       <c r="U9" t="n">
-        <v>-62.95481660382134</v>
+        <v>14.36766369510592</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.193108707808685</v>
       </c>
     </row>
     <row r="10">
@@ -1125,59 +1170,64 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F10" t="n">
-        <v>307.9612565172054</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G10" t="n">
-        <v>447.9094755317528</v>
+        <v>0.15</v>
       </c>
       <c r="H10" t="n">
-        <v>-139.9482190145474</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-45.44344980185151</v>
+        <v>395.9124372431456</v>
       </c>
       <c r="J10" t="n">
-        <v>4.118067446546455</v>
+        <v>332.4405794606201</v>
       </c>
       <c r="K10" t="n">
-        <v>-144.0662864610939</v>
+        <v>44.54817324850107</v>
       </c>
       <c r="L10" t="n">
-        <v>-46.78065289457769</v>
+        <v>63.47185778252543</v>
       </c>
       <c r="M10" t="n">
-        <v>8.23613489309291</v>
+        <v>16.03179183369398</v>
       </c>
       <c r="N10" t="n">
-        <v>-148.1843539076403</v>
+        <v>8.106429160680095</v>
       </c>
       <c r="O10" t="n">
-        <v>-48.11785598730386</v>
+        <v>27.91983584321486</v>
       </c>
       <c r="P10" t="n">
-        <v>12.35420233963936</v>
+        <v>35.84519851622878</v>
       </c>
       <c r="Q10" t="n">
-        <v>-152.3024213541868</v>
+        <v>4.831443232467795</v>
       </c>
       <c r="R10" t="n">
-        <v>-49.45505908003003</v>
+        <v>14.81146057405724</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9.733103054457958</v>
       </c>
       <c r="T10" t="n">
-        <v>13.58343774139322</v>
+        <v>13.57339393080606</v>
       </c>
       <c r="U10" t="n">
-        <v>-153.5316567559406</v>
+        <v>14.70599994146953</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12.31733415111353</v>
       </c>
     </row>
     <row r="11">
@@ -1198,59 +1248,64 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F11" t="n">
-        <v>362.307360608477</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G11" t="n">
-        <v>1381.620473865086</v>
+        <v>0.15</v>
       </c>
       <c r="H11" t="n">
-        <v>-1019.313113256609</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-281.3393334169983</v>
+        <v>341.9243139347174</v>
       </c>
       <c r="J11" t="n">
-        <v>12.70258078409988</v>
+        <v>340.333219456832</v>
       </c>
       <c r="K11" t="n">
-        <v>-1032.015694040709</v>
+        <v>34.89704502667647</v>
       </c>
       <c r="L11" t="n">
-        <v>-284.8453568007811</v>
+        <v>1.591094477885406</v>
       </c>
       <c r="M11" t="n">
-        <v>25.40516156819976</v>
+        <v>0.4653352841673579</v>
       </c>
       <c r="N11" t="n">
-        <v>-1044.718274824809</v>
+        <v>-8.379332508376777</v>
       </c>
       <c r="O11" t="n">
-        <v>-288.3513801845641</v>
+        <v>13.73233697298358</v>
       </c>
       <c r="P11" t="n">
-        <v>38.10774235229965</v>
+        <v>22.57700476552771</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1057.420855608909</v>
+        <v>4.946148970731975</v>
       </c>
       <c r="R11" t="n">
-        <v>-291.857403568347</v>
+        <v>-0.981227235418871</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.964181578564448</v>
       </c>
       <c r="T11" t="n">
-        <v>41.89943886920555</v>
+        <v>-2.448813014881911</v>
       </c>
       <c r="U11" t="n">
-        <v>-1061.212552125815</v>
+        <v>15.05514252662159</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-3.937727590588027</v>
       </c>
     </row>
     <row r="12">
@@ -1271,59 +1326,64 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F12" t="n">
-        <v>398.5380966693247</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G12" t="n">
-        <v>1381.620473865086</v>
+        <v>0.15</v>
       </c>
       <c r="H12" t="n">
-        <v>-983.0823771957616</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="n">
-        <v>-246.6721212881802</v>
+        <v>375.7106465934201</v>
       </c>
       <c r="J12" t="n">
-        <v>12.70258078409988</v>
+        <v>346.4992251670452</v>
       </c>
       <c r="K12" t="n">
-        <v>-995.7849579798615</v>
+        <v>39.20480244066107</v>
       </c>
       <c r="L12" t="n">
-        <v>-249.8594152734374</v>
+        <v>29.2114214263749</v>
       </c>
       <c r="M12" t="n">
-        <v>25.40516156819976</v>
+        <v>7.774978348693535</v>
       </c>
       <c r="N12" t="n">
-        <v>-1008.487538763961</v>
+        <v>-0.4092093867733344</v>
       </c>
       <c r="O12" t="n">
-        <v>-253.0467092586946</v>
+        <v>20.05125995189387</v>
       </c>
       <c r="P12" t="n">
-        <v>38.10774235229965</v>
+        <v>28.23544768736074</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1021.190119548061</v>
+        <v>5.03576109512516</v>
       </c>
       <c r="R12" t="n">
-        <v>-256.2340032439518</v>
+        <v>6.434648725142922</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>10.14470818307601</v>
       </c>
       <c r="T12" t="n">
-        <v>41.89943886920555</v>
+        <v>5.074839751329209</v>
       </c>
       <c r="U12" t="n">
-        <v>-1024.981816064967</v>
+        <v>15.32790489444269</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.695268328916009</v>
       </c>
     </row>
     <row r="13">
@@ -1344,59 +1404,64 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F13" t="n">
-        <v>307.9612565172054</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G13" t="n">
-        <v>1381.620473865086</v>
+        <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>-1073.659217347881</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-348.6345099023509</v>
+        <v>417.6194372431456</v>
       </c>
       <c r="J13" t="n">
-        <v>12.70258078409988</v>
+        <v>354.1475794606201</v>
       </c>
       <c r="K13" t="n">
-        <v>-1086.361798131981</v>
+        <v>44.54817324850107</v>
       </c>
       <c r="L13" t="n">
-        <v>-352.7592432950368</v>
+        <v>63.47185778252543</v>
       </c>
       <c r="M13" t="n">
-        <v>25.40516156819976</v>
+        <v>15.19849224488346</v>
       </c>
       <c r="N13" t="n">
-        <v>-1099.064378916081</v>
+        <v>7.685073634336545</v>
       </c>
       <c r="O13" t="n">
-        <v>-356.8839766877225</v>
+        <v>26.46862016070387</v>
       </c>
       <c r="P13" t="n">
-        <v>38.10774235229965</v>
+        <v>33.98203877125082</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1111.766959700181</v>
+        <v>5.146916567333648</v>
       </c>
       <c r="R13" t="n">
-        <v>-361.0087100804083</v>
+        <v>13.96605043103728</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>10.36863457815435</v>
       </c>
       <c r="T13" t="n">
-        <v>41.89943886920555</v>
+        <v>12.71569722782166</v>
       </c>
       <c r="U13" t="n">
-        <v>-1115.558656217087</v>
+        <v>15.66624114080631</v>
+      </c>
+      <c r="V13" t="n">
+        <v>11.44717232447345</v>
       </c>
     </row>
     <row r="14">
@@ -1417,59 +1482,64 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4940.554917388322</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G14" t="n">
-        <v>3194.85800959966</v>
+        <v>0.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1745.696907788662</v>
+        <v>0.75</v>
       </c>
       <c r="I14" t="n">
-        <v>35.33402496235125</v>
+        <v>4164.652592039076</v>
       </c>
       <c r="J14" t="n">
-        <v>29.37343700990284</v>
+        <v>3678.732684246563</v>
       </c>
       <c r="K14" t="n">
-        <v>1716.323470778759</v>
+        <v>839.7684632087922</v>
       </c>
       <c r="L14" t="n">
-        <v>34.73948775952566</v>
+        <v>485.9199077925132</v>
       </c>
       <c r="M14" t="n">
-        <v>58.74687401980569</v>
+        <v>11.66771770402581</v>
       </c>
       <c r="N14" t="n">
-        <v>1686.950033768856</v>
+        <v>1.93146697490095</v>
       </c>
       <c r="O14" t="n">
-        <v>34.14495055670007</v>
+        <v>21.40396843315066</v>
       </c>
       <c r="P14" t="n">
-        <v>88.12031102970853</v>
+        <v>26.2720937977131</v>
       </c>
       <c r="Q14" t="n">
-        <v>1657.576596758953</v>
+        <v>53.46395485231833</v>
       </c>
       <c r="R14" t="n">
-        <v>33.55041335387447</v>
+        <v>10.38396224854035</v>
       </c>
       <c r="S14" t="n">
-        <v>1782.934261864001</v>
+        <v>107.7049149164293</v>
       </c>
       <c r="T14" t="n">
-        <v>96.88822683303997</v>
+        <v>9.081549649520806</v>
       </c>
       <c r="U14" t="n">
-        <v>1648.808680955622</v>
+        <v>162.7341726060866</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.760208757969654</v>
       </c>
     </row>
     <row r="15">
@@ -1490,59 +1560,64 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5434.610409127155</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G15" t="n">
-        <v>3194.85800959966</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2239.752399527496</v>
+        <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>41.21274996577388</v>
+        <v>4625.375310112296</v>
       </c>
       <c r="J15" t="n">
-        <v>29.37343700990284</v>
+        <v>3807.735045307065</v>
       </c>
       <c r="K15" t="n">
-        <v>2210.378962517593</v>
+        <v>943.4310747752666</v>
       </c>
       <c r="L15" t="n">
-        <v>40.6722615995688</v>
+        <v>817.6402648052308</v>
       </c>
       <c r="M15" t="n">
-        <v>58.74687401980569</v>
+        <v>17.67727395045441</v>
       </c>
       <c r="N15" t="n">
-        <v>2181.00552550769</v>
+        <v>8.612005257913703</v>
       </c>
       <c r="O15" t="n">
-        <v>40.13177323336372</v>
+        <v>26.74254264299514</v>
       </c>
       <c r="P15" t="n">
-        <v>88.12031102970853</v>
+        <v>31.2751769892655</v>
       </c>
       <c r="Q15" t="n">
-        <v>2151.632088497787</v>
+        <v>55.33877887449208</v>
       </c>
       <c r="R15" t="n">
-        <v>39.59128486715863</v>
+        <v>16.48085689963679</v>
       </c>
       <c r="S15" t="n">
-        <v>2287.528421109584</v>
+        <v>111.4818102536575</v>
       </c>
       <c r="T15" t="n">
-        <v>96.88822683303997</v>
+        <v>15.267052016465</v>
       </c>
       <c r="U15" t="n">
-        <v>2142.864172694456</v>
+        <v>168.440782543066</v>
+      </c>
+      <c r="V15" t="n">
+        <v>14.03560659916273</v>
       </c>
     </row>
     <row r="16">
@@ -1563,59 +1638,64 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4199.471679780074</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G16" t="n">
-        <v>3194.85800959966</v>
+        <v>0.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1004.613670180414</v>
+        <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>23.92238230864854</v>
+        <v>5196.858818972188</v>
       </c>
       <c r="J16" t="n">
-        <v>29.37343700990284</v>
+        <v>3967.750427787835</v>
       </c>
       <c r="K16" t="n">
-        <v>975.240233170511</v>
+        <v>1072.014864268742</v>
       </c>
       <c r="L16" t="n">
-        <v>23.22292677591254</v>
+        <v>1229.108391184353</v>
       </c>
       <c r="M16" t="n">
-        <v>58.74687401980569</v>
+        <v>23.65098675948716</v>
       </c>
       <c r="N16" t="n">
-        <v>945.8667961606083</v>
+        <v>15.25269809379212</v>
       </c>
       <c r="O16" t="n">
-        <v>22.52347124317655</v>
+        <v>32.04927542518221</v>
       </c>
       <c r="P16" t="n">
-        <v>88.12031102970853</v>
+        <v>36.24841975802975</v>
       </c>
       <c r="Q16" t="n">
-        <v>916.4933591507054</v>
+        <v>57.66432300039816</v>
       </c>
       <c r="R16" t="n">
-        <v>21.82401571044056</v>
+        <v>22.54138719157351</v>
       </c>
       <c r="S16" t="n">
-        <v>1026.043022995629</v>
+        <v>116.1666962278992</v>
       </c>
       <c r="T16" t="n">
-        <v>96.88822683303997</v>
+        <v>21.41566153179752</v>
       </c>
       <c r="U16" t="n">
-        <v>907.7254433473739</v>
+        <v>175.5192992789424</v>
+      </c>
+      <c r="V16" t="n">
+        <v>20.27357541557739</v>
       </c>
     </row>
     <row r="17">
@@ -1636,59 +1716,64 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4940.554917388322</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G17" t="n">
-        <v>4128.569007932993</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="n">
-        <v>811.9859094553285</v>
+        <v>0.75</v>
       </c>
       <c r="I17" t="n">
-        <v>16.43511554942012</v>
+        <v>5915.821747594631</v>
       </c>
       <c r="J17" t="n">
-        <v>37.95795034745628</v>
+        <v>5429.901839802118</v>
       </c>
       <c r="K17" t="n">
-        <v>774.0279591078722</v>
+        <v>839.7684632087922</v>
       </c>
       <c r="L17" t="n">
-        <v>15.66682229123038</v>
+        <v>485.9199077925132</v>
       </c>
       <c r="M17" t="n">
-        <v>75.91590069491255</v>
+        <v>8.213903807870611</v>
       </c>
       <c r="N17" t="n">
-        <v>736.0700087604159</v>
+        <v>1.359724698725019</v>
       </c>
       <c r="O17" t="n">
-        <v>14.89852903304064</v>
+        <v>15.06808291701617</v>
       </c>
       <c r="P17" t="n">
-        <v>113.8738510423688</v>
+        <v>18.49517247158895</v>
       </c>
       <c r="Q17" t="n">
-        <v>698.1120584129596</v>
+        <v>78.91414020346454</v>
       </c>
       <c r="R17" t="n">
-        <v>14.13023577485089</v>
+        <v>6.879953199308902</v>
       </c>
       <c r="S17" t="n">
-        <v>641.7516504626625</v>
+        <v>158.9751596153902</v>
       </c>
       <c r="T17" t="n">
-        <v>125.2042279608523</v>
+        <v>5.526615948326342</v>
       </c>
       <c r="U17" t="n">
-        <v>686.7816814944762</v>
+        <v>240.1997261221062</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.15361030393312</v>
       </c>
     </row>
     <row r="18">
@@ -1709,59 +1794,64 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5434.610409127155</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G18" t="n">
-        <v>4128.569007932993</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1306.041401194162</v>
+        <v>0.75</v>
       </c>
       <c r="I18" t="n">
-        <v>24.03192322674558</v>
+        <v>6376.544465667852</v>
       </c>
       <c r="J18" t="n">
-        <v>37.95795034745628</v>
+        <v>5558.90420086262</v>
       </c>
       <c r="K18" t="n">
-        <v>1268.083450846706</v>
+        <v>943.4310747752666</v>
       </c>
       <c r="L18" t="n">
-        <v>23.33347481020945</v>
+        <v>817.6402648052317</v>
       </c>
       <c r="M18" t="n">
-        <v>75.91590069491255</v>
+        <v>12.82262311832864</v>
       </c>
       <c r="N18" t="n">
-        <v>1230.125500499249</v>
+        <v>6.246918955083204</v>
       </c>
       <c r="O18" t="n">
-        <v>22.63502639367332</v>
+        <v>19.39832728157408</v>
       </c>
       <c r="P18" t="n">
-        <v>113.8738510423688</v>
+        <v>22.68617936319682</v>
       </c>
       <c r="Q18" t="n">
-        <v>1192.167550151793</v>
+        <v>80.78896422563828</v>
       </c>
       <c r="R18" t="n">
-        <v>21.93657797713719</v>
+        <v>11.55565219605849</v>
       </c>
       <c r="S18" t="n">
-        <v>1032.227548568111</v>
+        <v>162.7520549526184</v>
       </c>
       <c r="T18" t="n">
-        <v>125.2042279608523</v>
+        <v>10.27026806413124</v>
       </c>
       <c r="U18" t="n">
-        <v>1180.83717323331</v>
+        <v>245.9063360590856</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.966203118702239</v>
       </c>
     </row>
     <row r="19">
@@ -1782,59 +1872,64 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4199.471679780074</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G19" t="n">
-        <v>4128.569007932993</v>
+        <v>0.3</v>
       </c>
       <c r="H19" t="n">
-        <v>70.90267184708046</v>
+        <v>0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>1.688371234611912</v>
+        <v>6948.027974527744</v>
       </c>
       <c r="J19" t="n">
-        <v>37.95795034745628</v>
+        <v>5718.91958334339</v>
       </c>
       <c r="K19" t="n">
-        <v>32.94472149962418</v>
+        <v>1072.014864268742</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7844968132122156</v>
+        <v>1229.108391184354</v>
       </c>
       <c r="M19" t="n">
-        <v>75.91590069491255</v>
+        <v>17.69003227520679</v>
       </c>
       <c r="N19" t="n">
-        <v>-5.013228847832096</v>
+        <v>11.40843400349601</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1193776081874813</v>
+        <v>23.97163054691755</v>
       </c>
       <c r="P19" t="n">
-        <v>113.8738510423688</v>
+        <v>27.11242968277294</v>
       </c>
       <c r="Q19" t="n">
-        <v>-42.97117919528836</v>
+        <v>83.11450835154436</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.023252029587178</v>
+        <v>16.49380064435769</v>
       </c>
       <c r="S19" t="n">
-        <v>56.03780330449161</v>
+        <v>167.43694092686</v>
       </c>
       <c r="T19" t="n">
-        <v>125.2042279608523</v>
+        <v>15.28018387590986</v>
       </c>
       <c r="U19" t="n">
-        <v>-54.30155611377185</v>
+        <v>252.9848527949619</v>
+      </c>
+      <c r="V19" t="n">
+        <v>14.04892930725051</v>
       </c>
     </row>
     <row r="20">
@@ -1855,59 +1950,64 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10292.822744559</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G20" t="n">
-        <v>6406.218705902068</v>
+        <v>0.3</v>
       </c>
       <c r="H20" t="n">
-        <v>3886.604038656936</v>
+        <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>37.76033198192862</v>
+        <v>16458.43391859993</v>
       </c>
       <c r="J20" t="n">
-        <v>58.89859926922235</v>
+        <v>16459.80332326033</v>
       </c>
       <c r="K20" t="n">
-        <v>3827.705439387713</v>
+        <v>2029.440452754581</v>
       </c>
       <c r="L20" t="n">
-        <v>37.18810217936684</v>
+        <v>-1.369404660403234</v>
       </c>
       <c r="M20" t="n">
-        <v>117.7971985384447</v>
+        <v>-0.008320382529565275</v>
       </c>
       <c r="N20" t="n">
-        <v>3768.806840118491</v>
+        <v>-3.087904232695319</v>
       </c>
       <c r="O20" t="n">
-        <v>36.61587237680508</v>
+        <v>3.584527442663799</v>
       </c>
       <c r="P20" t="n">
-        <v>176.695797807667</v>
+        <v>13.84980694321624</v>
       </c>
       <c r="Q20" t="n">
-        <v>3709.908240849269</v>
+        <v>239.2144951225405</v>
       </c>
       <c r="R20" t="n">
-        <v>36.04364257424331</v>
+        <v>-1.461766660016517</v>
       </c>
       <c r="S20" t="n">
-        <v>1979.641665614903</v>
+        <v>481.9055551561501</v>
       </c>
       <c r="T20" t="n">
-        <v>194.2769191164399</v>
+        <v>-2.936336240779245</v>
       </c>
       <c r="U20" t="n">
-        <v>3692.327119540496</v>
+        <v>728.1237059001692</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-4.4323361151401</v>
       </c>
     </row>
     <row r="21">
@@ -1928,59 +2028,64 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F21" t="n">
-        <v>11322.10501901491</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G21" t="n">
-        <v>6406.218705902068</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>4915.886313112839</v>
+        <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>43.41848361993512</v>
+        <v>17418.2729145858</v>
       </c>
       <c r="J21" t="n">
-        <v>58.89859926922235</v>
+        <v>16763.11244599186</v>
       </c>
       <c r="K21" t="n">
-        <v>4856.987713843617</v>
+        <v>2279.958430706894</v>
       </c>
       <c r="L21" t="n">
-        <v>42.89827470851533</v>
+        <v>655.1604685939383</v>
       </c>
       <c r="M21" t="n">
-        <v>117.7971985384447</v>
+        <v>3.761340012334498</v>
       </c>
       <c r="N21" t="n">
-        <v>4798.089114574394</v>
+        <v>0.7522680024669123</v>
       </c>
       <c r="O21" t="n">
-        <v>42.37806579709554</v>
+        <v>7.271924023846672</v>
       </c>
       <c r="P21" t="n">
-        <v>176.695797807667</v>
+        <v>17.30216405673863</v>
       </c>
       <c r="Q21" t="n">
-        <v>4739.190515305172</v>
+        <v>243.6225635080085</v>
       </c>
       <c r="R21" t="n">
-        <v>41.85785688567576</v>
+        <v>2.362679165173225</v>
       </c>
       <c r="S21" t="n">
-        <v>2503.906565235577</v>
+        <v>490.7857555026092</v>
       </c>
       <c r="T21" t="n">
-        <v>194.2769191164399</v>
+        <v>0.9436912252860851</v>
       </c>
       <c r="U21" t="n">
-        <v>4721.609393996399</v>
+        <v>741.541032835329</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.4959192261194675</v>
       </c>
     </row>
     <row r="22">
@@ -2001,59 +2106,64 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8748.899332875153</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G22" t="n">
-        <v>6406.218705902068</v>
+        <v>0.3</v>
       </c>
       <c r="H22" t="n">
-        <v>2342.680626973085</v>
+        <v>0.87</v>
       </c>
       <c r="I22" t="n">
-        <v>26.77686115521013</v>
+        <v>18608.86355804391</v>
       </c>
       <c r="J22" t="n">
-        <v>58.89859926922235</v>
+        <v>17139.33908932463</v>
       </c>
       <c r="K22" t="n">
-        <v>2283.782027703863</v>
+        <v>2590.702588649461</v>
       </c>
       <c r="L22" t="n">
-        <v>26.10364962278452</v>
+        <v>1469.524468719283</v>
       </c>
       <c r="M22" t="n">
-        <v>117.7971985384447</v>
+        <v>7.896906031556466</v>
       </c>
       <c r="N22" t="n">
-        <v>2224.88342843464</v>
+        <v>4.965190159946594</v>
       </c>
       <c r="O22" t="n">
-        <v>25.43043809035892</v>
+        <v>11.31724121510127</v>
       </c>
       <c r="P22" t="n">
-        <v>176.695797807667</v>
+        <v>21.08962745380076</v>
       </c>
       <c r="Q22" t="n">
-        <v>2165.984829165418</v>
+        <v>249.0903607087995</v>
       </c>
       <c r="R22" t="n">
-        <v>24.75722655793331</v>
+        <v>6.558348413935978</v>
       </c>
       <c r="S22" t="n">
-        <v>1193.244316183896</v>
+        <v>501.8008147872845</v>
       </c>
       <c r="T22" t="n">
-        <v>194.2769191164399</v>
+        <v>5.200337199063871</v>
       </c>
       <c r="U22" t="n">
-        <v>2148.403707856645</v>
+        <v>758.1839739702763</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.822589662878799</v>
       </c>
     </row>
     <row r="23">
@@ -2074,59 +2184,64 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10292.822744559</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G23" t="n">
-        <v>7339.929704235402</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>2952.893040323602</v>
+        <v>0.87</v>
       </c>
       <c r="I23" t="n">
-        <v>28.68885546372166</v>
+        <v>16458.43391859993</v>
       </c>
       <c r="J23" t="n">
-        <v>67.48311260677578</v>
+        <v>16459.80332326033</v>
       </c>
       <c r="K23" t="n">
-        <v>2885.409927716826</v>
+        <v>2029.440452754581</v>
       </c>
       <c r="L23" t="n">
-        <v>28.03322275458511</v>
+        <v>-1.369404660403234</v>
       </c>
       <c r="M23" t="n">
-        <v>134.9662252135516</v>
+        <v>-0.008320382529565275</v>
       </c>
       <c r="N23" t="n">
-        <v>2817.92681511005</v>
+        <v>-3.087904232695319</v>
       </c>
       <c r="O23" t="n">
-        <v>27.37759004544855</v>
+        <v>3.584527442663799</v>
       </c>
       <c r="P23" t="n">
-        <v>202.4493378203273</v>
+        <v>13.84980694321624</v>
       </c>
       <c r="Q23" t="n">
-        <v>2750.443702503274</v>
+        <v>239.2144951225405</v>
       </c>
       <c r="R23" t="n">
-        <v>26.72195733631199</v>
+        <v>-1.461766660016517</v>
       </c>
       <c r="S23" t="n">
-        <v>1312.725329163512</v>
+        <v>481.9055551561501</v>
       </c>
       <c r="T23" t="n">
-        <v>222.5929202442522</v>
+        <v>-2.936336240779245</v>
       </c>
       <c r="U23" t="n">
-        <v>2730.30012007935</v>
+        <v>728.1237059001692</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-4.4323361151401</v>
       </c>
     </row>
     <row r="24">
@@ -2147,59 +2262,64 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F24" t="n">
-        <v>11322.10501901491</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G24" t="n">
-        <v>7339.929704235402</v>
+        <v>0.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3982.175314779505</v>
+        <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>35.17168678520153</v>
+        <v>17418.2729145858</v>
       </c>
       <c r="J24" t="n">
-        <v>67.48311260677578</v>
+        <v>16763.11244599186</v>
       </c>
       <c r="K24" t="n">
-        <v>3914.69220217273</v>
+        <v>2279.958430706894</v>
       </c>
       <c r="L24" t="n">
-        <v>34.57565704962284</v>
+        <v>655.1604685939383</v>
       </c>
       <c r="M24" t="n">
-        <v>134.9662252135516</v>
+        <v>3.761340012334498</v>
       </c>
       <c r="N24" t="n">
-        <v>3847.209089565953</v>
+        <v>0.7522680024669123</v>
       </c>
       <c r="O24" t="n">
-        <v>33.97962731404415</v>
+        <v>7.271924023846672</v>
       </c>
       <c r="P24" t="n">
-        <v>202.4493378203273</v>
+        <v>17.30216405673863</v>
       </c>
       <c r="Q24" t="n">
-        <v>3779.725976959178</v>
+        <v>243.6225635080085</v>
       </c>
       <c r="R24" t="n">
-        <v>33.38359757846547</v>
+        <v>2.362679165173225</v>
       </c>
       <c r="S24" t="n">
-        <v>1770.298595139045</v>
+        <v>490.7857555026092</v>
       </c>
       <c r="T24" t="n">
-        <v>222.5929202442522</v>
+        <v>0.9436912252860851</v>
       </c>
       <c r="U24" t="n">
-        <v>3759.582394535253</v>
+        <v>741.541032835329</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.4959192261194675</v>
       </c>
     </row>
     <row r="25">
@@ -2220,59 +2340,64 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8748.899332875153</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G25" t="n">
-        <v>7339.929704235402</v>
+        <v>0.3</v>
       </c>
       <c r="H25" t="n">
-        <v>1408.969628639751</v>
+        <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>16.10453583967254</v>
+        <v>18608.86355804391</v>
       </c>
       <c r="J25" t="n">
-        <v>67.48311260677578</v>
+        <v>17139.33908932463</v>
       </c>
       <c r="K25" t="n">
-        <v>1341.486516032975</v>
+        <v>2590.702588649461</v>
       </c>
       <c r="L25" t="n">
-        <v>15.33320324068836</v>
+        <v>1469.524468719283</v>
       </c>
       <c r="M25" t="n">
-        <v>134.9662252135516</v>
+        <v>7.896906031556466</v>
       </c>
       <c r="N25" t="n">
-        <v>1274.0034034262</v>
+        <v>4.965190159946594</v>
       </c>
       <c r="O25" t="n">
-        <v>14.56187064170418</v>
+        <v>11.31724121510127</v>
       </c>
       <c r="P25" t="n">
-        <v>202.4493378203273</v>
+        <v>21.08962745380076</v>
       </c>
       <c r="Q25" t="n">
-        <v>1206.520290819424</v>
+        <v>249.0903607087995</v>
       </c>
       <c r="R25" t="n">
-        <v>13.79053804271999</v>
+        <v>6.558348413935978</v>
       </c>
       <c r="S25" t="n">
-        <v>626.365430200213</v>
+        <v>501.8008147872845</v>
       </c>
       <c r="T25" t="n">
-        <v>222.5929202442522</v>
+        <v>5.200337199063871</v>
       </c>
       <c r="U25" t="n">
-        <v>1186.376708395499</v>
+        <v>758.1839739702763</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3.822589662878799</v>
       </c>
     </row>
     <row r="26">
@@ -2293,59 +2418,64 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F26" t="n">
-        <v>115279.6147390609</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G26" t="n">
-        <v>69398.29390260318</v>
+        <v>0.65</v>
       </c>
       <c r="H26" t="n">
-        <v>45881.32083645767</v>
+        <v>0.55</v>
       </c>
       <c r="I26" t="n">
-        <v>39.80002964124363</v>
+        <v>87357.31758276363</v>
       </c>
       <c r="J26" t="n">
-        <v>638.046012817413</v>
+        <v>55027.3260022231</v>
       </c>
       <c r="K26" t="n">
-        <v>45243.27482364025</v>
+        <v>31133.63821007411</v>
       </c>
       <c r="L26" t="n">
-        <v>39.24655276307946</v>
+        <v>32329.99158054053</v>
       </c>
       <c r="M26" t="n">
-        <v>1276.092025634826</v>
+        <v>37.00891061577138</v>
       </c>
       <c r="N26" t="n">
-        <v>44605.22881082285</v>
+        <v>21.40924399370883</v>
       </c>
       <c r="O26" t="n">
-        <v>38.69307588491532</v>
+        <v>52.60857723783396</v>
       </c>
       <c r="P26" t="n">
-        <v>1914.138038452239</v>
+        <v>31.80902174175053</v>
       </c>
       <c r="Q26" t="n">
-        <v>43967.18279800543</v>
+        <v>799.7260811107839</v>
       </c>
       <c r="R26" t="n">
-        <v>38.13959900675118</v>
+        <v>36.09344514219716</v>
       </c>
       <c r="S26" t="n">
-        <v>2157.273296036755</v>
+        <v>1611.074784130965</v>
       </c>
       <c r="T26" t="n">
-        <v>2104.59357544467</v>
+        <v>35.16467497677686</v>
       </c>
       <c r="U26" t="n">
-        <v>43776.727261013</v>
+        <v>2434.215023571684</v>
+      </c>
+      <c r="V26" t="n">
+        <v>34.22240675905043</v>
       </c>
     </row>
     <row r="27">
@@ -2366,59 +2496,64 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F27" t="n">
-        <v>126807.576212967</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G27" t="n">
-        <v>69398.29390260318</v>
+        <v>0.65</v>
       </c>
       <c r="H27" t="n">
-        <v>57409.28231036378</v>
+        <v>0.55</v>
       </c>
       <c r="I27" t="n">
-        <v>45.2727542193124</v>
+        <v>98107.51433780542</v>
       </c>
       <c r="J27" t="n">
-        <v>638.046012817413</v>
+        <v>59461.78216367784</v>
       </c>
       <c r="K27" t="n">
-        <v>56771.23629754636</v>
+        <v>34976.83355000155</v>
       </c>
       <c r="L27" t="n">
-        <v>44.76959342098134</v>
+        <v>38645.73217412758</v>
       </c>
       <c r="M27" t="n">
-        <v>1276.092025634826</v>
+        <v>39.39120508247916</v>
       </c>
       <c r="N27" t="n">
-        <v>56133.19028472895</v>
+        <v>24.43251960811999</v>
       </c>
       <c r="O27" t="n">
-        <v>44.26643262265031</v>
+        <v>54.34989055683835</v>
       </c>
       <c r="P27" t="n">
-        <v>1914.138038452239</v>
+        <v>34.40497659102611</v>
       </c>
       <c r="Q27" t="n">
-        <v>55495.14427191154</v>
+        <v>864.1731568730061</v>
       </c>
       <c r="R27" t="n">
-        <v>43.76327182431925</v>
+        <v>38.51036209842651</v>
       </c>
       <c r="S27" t="n">
-        <v>2699.301358699612</v>
+        <v>1740.905561348184</v>
       </c>
       <c r="T27" t="n">
-        <v>2104.59357544467</v>
+        <v>37.61671759994661</v>
       </c>
       <c r="U27" t="n">
-        <v>55304.68873491911</v>
+        <v>2630.379740155351</v>
+      </c>
+      <c r="V27" t="n">
+        <v>36.71008553938444</v>
       </c>
     </row>
     <row r="28">
@@ -2439,59 +2574,64 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F28" t="n">
-        <v>97987.67252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G28" t="n">
-        <v>69398.29390260318</v>
+        <v>0.65</v>
       </c>
       <c r="H28" t="n">
-        <v>28589.37862559853</v>
+        <v>0.55</v>
       </c>
       <c r="I28" t="n">
-        <v>29.17650546028661</v>
+        <v>111442.1295445362</v>
       </c>
       <c r="J28" t="n">
-        <v>638.046012817413</v>
+        <v>64962.31093645431</v>
       </c>
       <c r="K28" t="n">
-        <v>27951.33261278112</v>
+        <v>39743.95848640782</v>
       </c>
       <c r="L28" t="n">
-        <v>28.5253561918582</v>
+        <v>46479.81860808193</v>
       </c>
       <c r="M28" t="n">
-        <v>1276.092025634826</v>
+        <v>41.70758293837785</v>
       </c>
       <c r="N28" t="n">
-        <v>27313.28659996371</v>
+        <v>27.37214306079015</v>
       </c>
       <c r="O28" t="n">
-        <v>27.87420692342979</v>
+        <v>56.04302281596556</v>
       </c>
       <c r="P28" t="n">
-        <v>1914.138038452239</v>
+        <v>36.92910297918194</v>
       </c>
       <c r="Q28" t="n">
-        <v>26675.24058714629</v>
+        <v>944.1137362010279</v>
       </c>
       <c r="R28" t="n">
-        <v>27.22305765500138</v>
+        <v>40.86040446102855</v>
       </c>
       <c r="S28" t="n">
-        <v>1344.231202042469</v>
+        <v>1901.948516712743</v>
       </c>
       <c r="T28" t="n">
-        <v>2104.59357544467</v>
+        <v>40.00091372406365</v>
       </c>
       <c r="U28" t="n">
-        <v>26484.78505015386</v>
+        <v>2873.7037529511</v>
+      </c>
+      <c r="V28" t="n">
+        <v>39.12893179029236</v>
       </c>
     </row>
     <row r="29">
@@ -2512,59 +2652,64 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F29" t="n">
-        <v>115279.6147390609</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G29" t="n">
-        <v>70332.00490093652</v>
+        <v>0.65</v>
       </c>
       <c r="H29" t="n">
-        <v>44947.60983812434</v>
+        <v>0.55</v>
       </c>
       <c r="I29" t="n">
-        <v>38.99007638068943</v>
+        <v>88451.79830498584</v>
       </c>
       <c r="J29" t="n">
-        <v>646.6305261549664</v>
+        <v>56121.80672444532</v>
       </c>
       <c r="K29" t="n">
-        <v>44300.97931196937</v>
+        <v>31133.63821007411</v>
       </c>
       <c r="L29" t="n">
-        <v>38.42915281443825</v>
+        <v>32329.99158054053</v>
       </c>
       <c r="M29" t="n">
-        <v>1293.261052309933</v>
+        <v>36.55097148965275</v>
       </c>
       <c r="N29" t="n">
-        <v>43654.3487858144</v>
+        <v>21.14433129235626</v>
       </c>
       <c r="O29" t="n">
-        <v>37.86822924818706</v>
+        <v>51.95761168694924</v>
       </c>
       <c r="P29" t="n">
-        <v>1939.8915784649</v>
+        <v>31.41542475722058</v>
       </c>
       <c r="Q29" t="n">
-        <v>43007.71825965944</v>
+        <v>815.6324469552503</v>
       </c>
       <c r="R29" t="n">
-        <v>37.30730568193587</v>
+        <v>35.628850670647</v>
       </c>
       <c r="S29" t="n">
-        <v>2085.314937359725</v>
+        <v>1643.118687067815</v>
       </c>
       <c r="T29" t="n">
-        <v>2132.909576572483</v>
+        <v>34.69332843597252</v>
       </c>
       <c r="U29" t="n">
-        <v>42814.70026155185</v>
+        <v>2482.630994519196</v>
+      </c>
+      <c r="V29" t="n">
+        <v>33.74421001945745</v>
       </c>
     </row>
     <row r="30">
@@ -2585,59 +2730,64 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F30" t="n">
-        <v>126807.576212967</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G30" t="n">
-        <v>70332.00490093652</v>
+        <v>0.65</v>
       </c>
       <c r="H30" t="n">
-        <v>56475.57131203044</v>
+        <v>0.55</v>
       </c>
       <c r="I30" t="n">
-        <v>44.53643307335404</v>
+        <v>99201.99506002764</v>
       </c>
       <c r="J30" t="n">
-        <v>646.6305261549664</v>
+        <v>60556.26288590006</v>
       </c>
       <c r="K30" t="n">
-        <v>55828.94078587548</v>
+        <v>34976.83355000155</v>
       </c>
       <c r="L30" t="n">
-        <v>44.02650255858023</v>
+        <v>38645.73217412757</v>
       </c>
       <c r="M30" t="n">
-        <v>1293.261052309933</v>
+        <v>38.95660782904905</v>
       </c>
       <c r="N30" t="n">
-        <v>55182.31025972051</v>
+        <v>24.1629592863722</v>
       </c>
       <c r="O30" t="n">
-        <v>43.51657204380642</v>
+        <v>53.75025637172591</v>
       </c>
       <c r="P30" t="n">
-        <v>1939.8915784649</v>
+        <v>34.02539164815677</v>
       </c>
       <c r="Q30" t="n">
-        <v>54535.67973356554</v>
+        <v>880.0795227174724</v>
       </c>
       <c r="R30" t="n">
-        <v>43.00664152903263</v>
+        <v>38.06944873291904</v>
       </c>
       <c r="S30" t="n">
-        <v>2620.14716415488</v>
+        <v>1772.949464285035</v>
       </c>
       <c r="T30" t="n">
-        <v>2132.909576572483</v>
+        <v>37.1693963287035</v>
       </c>
       <c r="U30" t="n">
-        <v>54342.66173545796</v>
+        <v>2678.795711102863</v>
+      </c>
+      <c r="V30" t="n">
+        <v>36.25626323468689</v>
       </c>
     </row>
     <row r="31">
@@ -2658,59 +2808,64 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F31" t="n">
-        <v>97987.67252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G31" t="n">
-        <v>70332.00490093652</v>
+        <v>0.65</v>
       </c>
       <c r="H31" t="n">
-        <v>27655.6676272652</v>
+        <v>0.55</v>
       </c>
       <c r="I31" t="n">
-        <v>28.22361927139932</v>
+        <v>112536.6102667584</v>
       </c>
       <c r="J31" t="n">
-        <v>646.6305261549664</v>
+        <v>66056.79165867652</v>
       </c>
       <c r="K31" t="n">
-        <v>27009.03710111023</v>
+        <v>39743.95848640782</v>
       </c>
       <c r="L31" t="n">
-        <v>27.56370919345675</v>
+        <v>46479.81860808193</v>
       </c>
       <c r="M31" t="n">
-        <v>1293.261052309933</v>
+        <v>41.30195364682256</v>
       </c>
       <c r="N31" t="n">
-        <v>26362.40657495526</v>
+        <v>27.10593384376353</v>
       </c>
       <c r="O31" t="n">
-        <v>26.90379911551418</v>
+        <v>55.4979734498816</v>
       </c>
       <c r="P31" t="n">
-        <v>1939.8915784649</v>
+        <v>36.56994704580288</v>
       </c>
       <c r="Q31" t="n">
-        <v>25715.7760488003</v>
+        <v>960.0201020454941</v>
       </c>
       <c r="R31" t="n">
-        <v>26.24388903757161</v>
+        <v>40.44888005613074</v>
       </c>
       <c r="S31" t="n">
-        <v>1283.066597166994</v>
+        <v>1933.992419649593</v>
       </c>
       <c r="T31" t="n">
-        <v>2132.909576572483</v>
+        <v>39.58340853064638</v>
       </c>
       <c r="U31" t="n">
-        <v>25522.75805069271</v>
+        <v>2922.119723898612</v>
+      </c>
+      <c r="V31" t="n">
+        <v>38.70535888803964</v>
       </c>
     </row>
     <row r="32">
@@ -2731,59 +2886,64 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F32" t="n">
-        <v>27996.47786520049</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G32" t="n">
-        <v>17028.41177828696</v>
+        <v>0.55</v>
       </c>
       <c r="H32" t="n">
-        <v>10968.06608691353</v>
+        <v>0.74</v>
       </c>
       <c r="I32" t="n">
-        <v>39.17659264041493</v>
+        <v>21612.95459192513</v>
       </c>
       <c r="J32" t="n">
-        <v>156.5587513577408</v>
+        <v>18146.64488791798</v>
       </c>
       <c r="K32" t="n">
-        <v>10811.50733555579</v>
+        <v>8607.937773246864</v>
       </c>
       <c r="L32" t="n">
-        <v>38.61738389954563</v>
+        <v>3466.309704007155</v>
       </c>
       <c r="M32" t="n">
-        <v>313.1175027154816</v>
+        <v>16.03811125991174</v>
       </c>
       <c r="N32" t="n">
-        <v>10654.94858419805</v>
+        <v>7.77470901392016</v>
       </c>
       <c r="O32" t="n">
-        <v>38.05817515867632</v>
+        <v>25.33443878665225</v>
       </c>
       <c r="P32" t="n">
-        <v>469.6762540732224</v>
+        <v>30.49906519039699</v>
       </c>
       <c r="Q32" t="n">
-        <v>10498.38983284031</v>
+        <v>263.7297912847407</v>
       </c>
       <c r="R32" t="n">
-        <v>37.49896641780703</v>
+        <v>14.81787184209853</v>
       </c>
       <c r="S32" t="n">
-        <v>2101.715680240299</v>
+        <v>531.2924344955926</v>
       </c>
       <c r="T32" t="n">
-        <v>516.4087474384553</v>
+        <v>13.57989837543138</v>
       </c>
       <c r="U32" t="n">
-        <v>10451.65733947508</v>
+        <v>802.7436334414224</v>
+      </c>
+      <c r="V32" t="n">
+        <v>12.32393312648181</v>
       </c>
     </row>
     <row r="33">
@@ -2804,59 +2964,64 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F33" t="n">
-        <v>30796.12565172055</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G33" t="n">
-        <v>17028.41177828696</v>
+        <v>0.55</v>
       </c>
       <c r="H33" t="n">
-        <v>13767.71387343359</v>
+        <v>0.74</v>
       </c>
       <c r="I33" t="n">
-        <v>44.70599330946813</v>
+        <v>24223.71666100671</v>
       </c>
       <c r="J33" t="n">
-        <v>156.5587513577408</v>
+        <v>19352.81696383367</v>
       </c>
       <c r="K33" t="n">
-        <v>13611.15512207584</v>
+        <v>9670.517935363065</v>
       </c>
       <c r="L33" t="n">
-        <v>44.19762172685967</v>
+        <v>4870.899697173041</v>
       </c>
       <c r="M33" t="n">
-        <v>313.1175027154816</v>
+        <v>20.10797833106182</v>
       </c>
       <c r="N33" t="n">
-        <v>13454.5963707181</v>
+        <v>12.26096239698893</v>
       </c>
       <c r="O33" t="n">
-        <v>43.68925014425121</v>
+        <v>28.93587125689385</v>
       </c>
       <c r="P33" t="n">
-        <v>469.6762540732224</v>
+        <v>33.84025621568941</v>
       </c>
       <c r="Q33" t="n">
-        <v>13298.03761936036</v>
+        <v>281.2593958920651</v>
       </c>
       <c r="R33" t="n">
-        <v>43.18087856164276</v>
+        <v>18.94688732331893</v>
       </c>
       <c r="S33" t="n">
-        <v>2638.18798132351</v>
+        <v>566.6064058986761</v>
       </c>
       <c r="T33" t="n">
-        <v>516.4087474384553</v>
+        <v>17.76892188556289</v>
       </c>
       <c r="U33" t="n">
-        <v>13251.30512599513</v>
+        <v>856.1004363521798</v>
+      </c>
+      <c r="V33" t="n">
+        <v>16.57383677742378</v>
       </c>
     </row>
     <row r="34">
@@ -2877,59 +3042,64 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F34" t="n">
-        <v>23797.00618542042</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G34" t="n">
-        <v>17028.41177828696</v>
+        <v>0.55</v>
       </c>
       <c r="H34" t="n">
-        <v>6768.594407133456</v>
+        <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>28.44305016519403</v>
+        <v>27462.12321121277</v>
       </c>
       <c r="J34" t="n">
-        <v>156.5587513577408</v>
+        <v>20848.96079002886</v>
       </c>
       <c r="K34" t="n">
-        <v>6612.035655775715</v>
+        <v>10988.54940129693</v>
       </c>
       <c r="L34" t="n">
-        <v>27.7851575288772</v>
+        <v>6613.162421183901</v>
       </c>
       <c r="M34" t="n">
-        <v>313.1175027154816</v>
+        <v>24.0810310634822</v>
       </c>
       <c r="N34" t="n">
-        <v>6455.476904417975</v>
+        <v>16.64049640886873</v>
       </c>
       <c r="O34" t="n">
-        <v>27.12726489256038</v>
+        <v>32.45163254992236</v>
       </c>
       <c r="P34" t="n">
-        <v>469.6762540732224</v>
+        <v>37.10196670905578</v>
       </c>
       <c r="Q34" t="n">
-        <v>6298.918153060234</v>
+        <v>303.0032334692871</v>
       </c>
       <c r="R34" t="n">
-        <v>26.46937225624355</v>
+        <v>22.97768143847734</v>
       </c>
       <c r="S34" t="n">
-        <v>1297.007228615482</v>
+        <v>610.410089757836</v>
       </c>
       <c r="T34" t="n">
-        <v>516.4087474384553</v>
+        <v>21.85829655361515</v>
       </c>
       <c r="U34" t="n">
-        <v>6252.185659695001</v>
+        <v>922.2845678326236</v>
+      </c>
+      <c r="V34" t="n">
+        <v>20.72264336439833</v>
       </c>
     </row>
     <row r="35">
@@ -2950,59 +3120,64 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F35" t="n">
-        <v>27996.47786520049</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G35" t="n">
-        <v>17962.12277662029</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="n">
-        <v>10034.3550885802</v>
+        <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>35.84149097930944</v>
+        <v>23489.2072585918</v>
       </c>
       <c r="J35" t="n">
-        <v>165.1432646952942</v>
+        <v>20022.89755458464</v>
       </c>
       <c r="K35" t="n">
-        <v>9869.211823884905</v>
+        <v>8607.937773246864</v>
       </c>
       <c r="L35" t="n">
-        <v>35.25161940514058</v>
+        <v>3466.309704007155</v>
       </c>
       <c r="M35" t="n">
-        <v>330.2865293905884</v>
+        <v>14.75703145639051</v>
       </c>
       <c r="N35" t="n">
-        <v>9704.068559189611</v>
+        <v>7.153686841509919</v>
       </c>
       <c r="O35" t="n">
-        <v>34.66174783097172</v>
+        <v>23.31079414813118</v>
       </c>
       <c r="P35" t="n">
-        <v>495.4297940858826</v>
+        <v>28.06288453243154</v>
       </c>
       <c r="Q35" t="n">
-        <v>9538.925294494316</v>
+        <v>290.9978470181117</v>
       </c>
       <c r="R35" t="n">
-        <v>34.07187625680287</v>
+        <v>13.51817378097164</v>
       </c>
       <c r="S35" t="n">
-        <v>1822.845474278576</v>
+        <v>586.2248395301935</v>
       </c>
       <c r="T35" t="n">
-        <v>544.7247485662676</v>
+        <v>12.26131147284034</v>
       </c>
       <c r="U35" t="n">
-        <v>9489.630340013931</v>
+        <v>885.7424407800149</v>
+      </c>
+      <c r="V35" t="n">
+        <v>10.9861828661043</v>
       </c>
     </row>
     <row r="36">
@@ -3023,59 +3198,64 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F36" t="n">
-        <v>30796.12565172055</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G36" t="n">
-        <v>17962.12277662029</v>
+        <v>0.55</v>
       </c>
       <c r="H36" t="n">
-        <v>12834.00287510025</v>
+        <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>41.67408270846314</v>
+        <v>26099.96932767337</v>
       </c>
       <c r="J36" t="n">
-        <v>165.1432646952942</v>
+        <v>21229.06963050033</v>
       </c>
       <c r="K36" t="n">
-        <v>12668.85961040496</v>
+        <v>9670.517935363065</v>
       </c>
       <c r="L36" t="n">
-        <v>41.13783582285508</v>
+        <v>4870.899697173041</v>
       </c>
       <c r="M36" t="n">
-        <v>330.2865293905884</v>
+        <v>18.66247287888</v>
       </c>
       <c r="N36" t="n">
-        <v>12503.71634570966</v>
+        <v>11.37955663346342</v>
       </c>
       <c r="O36" t="n">
-        <v>40.60158893724703</v>
+        <v>26.85575365497366</v>
       </c>
       <c r="P36" t="n">
-        <v>495.4297940858826</v>
+        <v>31.40757630835902</v>
       </c>
       <c r="Q36" t="n">
-        <v>12338.57308101437</v>
+        <v>308.5274516254361</v>
       </c>
       <c r="R36" t="n">
-        <v>40.06534205163897</v>
+        <v>17.48037397388891</v>
       </c>
       <c r="S36" t="n">
-        <v>2331.430754765616</v>
+        <v>621.5388109332772</v>
       </c>
       <c r="T36" t="n">
-        <v>544.7247485662676</v>
+        <v>16.28109532578736</v>
       </c>
       <c r="U36" t="n">
-        <v>12289.27812653399</v>
+        <v>939.0992436907724</v>
+      </c>
+      <c r="V36" t="n">
+        <v>15.06438725701277</v>
       </c>
     </row>
     <row r="37">
@@ -3096,59 +3276,64 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F37" t="n">
-        <v>23797.00618542042</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G37" t="n">
-        <v>17962.12277662029</v>
+        <v>0.55</v>
       </c>
       <c r="H37" t="n">
-        <v>5834.883408800124</v>
+        <v>0.74</v>
       </c>
       <c r="I37" t="n">
-        <v>24.51940115212875</v>
+        <v>29338.37587787943</v>
       </c>
       <c r="J37" t="n">
-        <v>165.1432646952942</v>
+        <v>22725.21345669553</v>
       </c>
       <c r="K37" t="n">
-        <v>5669.74014410483</v>
+        <v>10988.54940129693</v>
       </c>
       <c r="L37" t="n">
-        <v>23.82543459428303</v>
+        <v>6613.162421183901</v>
       </c>
       <c r="M37" t="n">
-        <v>330.2865293905884</v>
+        <v>22.54099698194301</v>
       </c>
       <c r="N37" t="n">
-        <v>5504.596879409535</v>
+        <v>15.57630063021496</v>
       </c>
       <c r="O37" t="n">
-        <v>23.13146803643732</v>
+        <v>30.3762803776371</v>
       </c>
       <c r="P37" t="n">
-        <v>495.4297940858826</v>
+        <v>34.72921559746715</v>
       </c>
       <c r="Q37" t="n">
-        <v>5339.453614714242</v>
+        <v>330.271289202658</v>
       </c>
       <c r="R37" t="n">
-        <v>22.4375014785916</v>
+        <v>21.41526565115154</v>
       </c>
       <c r="S37" t="n">
-        <v>1059.967553548018</v>
+        <v>665.342494792437</v>
       </c>
       <c r="T37" t="n">
-        <v>544.7247485662676</v>
+        <v>20.27317378149758</v>
       </c>
       <c r="U37" t="n">
-        <v>5290.158660233857</v>
+        <v>1005.283375171216</v>
+      </c>
+      <c r="V37" t="n">
+        <v>19.11448360112162</v>
       </c>
     </row>
     <row r="38">
@@ -3169,59 +3354,64 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F38" t="n">
-        <v>8645.971105429564</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G38" t="n">
-        <v>5418.107722424405</v>
+        <v>0.4</v>
       </c>
       <c r="H38" t="n">
-        <v>3227.863383005159</v>
+        <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>37.33372854991501</v>
+        <v>6693.663108290605</v>
       </c>
       <c r="J38" t="n">
-        <v>49.81393395866251</v>
+        <v>6063.445066730631</v>
       </c>
       <c r="K38" t="n">
-        <v>3178.049449046497</v>
+        <v>2063.964267353165</v>
       </c>
       <c r="L38" t="n">
-        <v>36.75757656708708</v>
+        <v>630.2180415599742</v>
       </c>
       <c r="M38" t="n">
-        <v>99.62786791732502</v>
+        <v>9.415144314320237</v>
       </c>
       <c r="N38" t="n">
-        <v>3128.235515087834</v>
+        <v>-0.01730262675851245</v>
       </c>
       <c r="O38" t="n">
-        <v>36.18142458425914</v>
+        <v>18.84759125539899</v>
       </c>
       <c r="P38" t="n">
-        <v>149.4418018759875</v>
+        <v>29.32808785659759</v>
       </c>
       <c r="Q38" t="n">
-        <v>3078.421581129172</v>
+        <v>88.12158455693631</v>
       </c>
       <c r="R38" t="n">
-        <v>35.60527260143122</v>
+        <v>8.098651638616388</v>
       </c>
       <c r="S38" t="n">
-        <v>1943.952099236187</v>
+        <v>177.523862445694</v>
       </c>
       <c r="T38" t="n">
-        <v>164.3111676446246</v>
+        <v>6.763026041056419</v>
       </c>
       <c r="U38" t="n">
-        <v>3063.552215360535</v>
+        <v>268.225446307186</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5.407989458035811</v>
       </c>
     </row>
     <row r="39">
@@ -3242,59 +3432,64 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F39" t="n">
-        <v>9510.568215972522</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G39" t="n">
-        <v>5418.107722424405</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="n">
-        <v>4092.460493548117</v>
+        <v>0.79</v>
       </c>
       <c r="I39" t="n">
-        <v>43.03066231810456</v>
+        <v>7499.92786491874</v>
       </c>
       <c r="J39" t="n">
-        <v>49.81393395866251</v>
+        <v>6362.569291439669</v>
       </c>
       <c r="K39" t="n">
-        <v>4042.646559589455</v>
+        <v>2318.743930447655</v>
       </c>
       <c r="L39" t="n">
-        <v>42.50688778826099</v>
+        <v>1137.358573479071</v>
       </c>
       <c r="M39" t="n">
-        <v>99.62786791732502</v>
+        <v>15.16492683615157</v>
       </c>
       <c r="N39" t="n">
-        <v>3992.832625630792</v>
+        <v>6.3594854474184</v>
       </c>
       <c r="O39" t="n">
-        <v>41.98311325841742</v>
+        <v>23.97036822488475</v>
       </c>
       <c r="P39" t="n">
-        <v>149.4418018759875</v>
+        <v>33.75419199014382</v>
       </c>
       <c r="Q39" t="n">
-        <v>3943.01869167213</v>
+        <v>92.46883275835165</v>
       </c>
       <c r="R39" t="n">
-        <v>41.45933872857384</v>
+        <v>13.93199720770969</v>
       </c>
       <c r="S39" t="n">
-        <v>2464.648042218988</v>
+        <v>186.2815385088919</v>
       </c>
       <c r="T39" t="n">
-        <v>164.3111676446246</v>
+        <v>12.68114910036517</v>
       </c>
       <c r="U39" t="n">
-        <v>3928.149325903493</v>
+        <v>281.457648098557</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11.41212210032086</v>
       </c>
     </row>
     <row r="40">
@@ -3315,59 +3510,64 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F40" t="n">
-        <v>7349.075439615129</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G40" t="n">
-        <v>5418.107722424405</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1930.967717190724</v>
+        <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>26.27497476460589</v>
+        <v>8500.024005423551</v>
       </c>
       <c r="J40" t="n">
-        <v>49.81393395866251</v>
+        <v>6733.604959566954</v>
       </c>
       <c r="K40" t="n">
-        <v>1881.153783232062</v>
+        <v>2634.774310847175</v>
       </c>
       <c r="L40" t="n">
-        <v>25.59714890245538</v>
+        <v>1766.419045856597</v>
       </c>
       <c r="M40" t="n">
-        <v>99.62786791732502</v>
+        <v>20.78134184949961</v>
       </c>
       <c r="N40" t="n">
-        <v>1831.339849273399</v>
+        <v>12.58836247724714</v>
       </c>
       <c r="O40" t="n">
-        <v>24.91932304030487</v>
+        <v>28.97432122175209</v>
       </c>
       <c r="P40" t="n">
-        <v>149.4418018759875</v>
+        <v>38.07763163536594</v>
       </c>
       <c r="Q40" t="n">
-        <v>1781.525915314737</v>
+        <v>97.8611882002964</v>
       </c>
       <c r="R40" t="n">
-        <v>24.24149717815436</v>
+        <v>19.63003700450323</v>
       </c>
       <c r="S40" t="n">
-        <v>1162.908184761987</v>
+        <v>197.1446178616648</v>
       </c>
       <c r="T40" t="n">
-        <v>164.3111676446246</v>
+        <v>18.46199995427821</v>
       </c>
       <c r="U40" t="n">
-        <v>1766.6565495461</v>
+        <v>297.8709587798703</v>
+      </c>
+      <c r="V40" t="n">
+        <v>17.27698752544347</v>
       </c>
     </row>
     <row r="41">
@@ -3388,59 +3588,64 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F41" t="n">
-        <v>8645.971105429564</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G41" t="n">
-        <v>6351.818720757738</v>
+        <v>0.4</v>
       </c>
       <c r="H41" t="n">
-        <v>2294.152384671826</v>
+        <v>0.79</v>
       </c>
       <c r="I41" t="n">
-        <v>26.53435174252579</v>
+        <v>7350.351541623939</v>
       </c>
       <c r="J41" t="n">
-        <v>58.39844729621594</v>
+        <v>6720.133500063965</v>
       </c>
       <c r="K41" t="n">
-        <v>2235.753937375609</v>
+        <v>2063.964267353165</v>
       </c>
       <c r="L41" t="n">
-        <v>25.85891058520405</v>
+        <v>630.2180415599742</v>
       </c>
       <c r="M41" t="n">
-        <v>116.7968945924319</v>
+        <v>8.573985039914675</v>
       </c>
       <c r="N41" t="n">
-        <v>2177.355490079394</v>
+        <v>-0.01575679118938965</v>
       </c>
       <c r="O41" t="n">
-        <v>25.18346942788233</v>
+        <v>17.16372687101874</v>
       </c>
       <c r="P41" t="n">
-        <v>175.1953418886478</v>
+        <v>26.70788446113436</v>
       </c>
       <c r="Q41" t="n">
-        <v>2118.957042783178</v>
+        <v>97.66540406361615</v>
       </c>
       <c r="R41" t="n">
-        <v>24.50802827056059</v>
+        <v>7.245267583197787</v>
       </c>
       <c r="S41" t="n">
-        <v>1178.53427148592</v>
+        <v>196.7502042078044</v>
       </c>
       <c r="T41" t="n">
-        <v>192.6271687724369</v>
+        <v>5.897239538782689</v>
       </c>
       <c r="U41" t="n">
-        <v>2101.525215899389</v>
+        <v>297.2750288756934</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4.529620261002135</v>
       </c>
     </row>
     <row r="42">
@@ -3461,59 +3666,64 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F42" t="n">
-        <v>9510.568215972522</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G42" t="n">
-        <v>6351.818720757738</v>
+        <v>0.4</v>
       </c>
       <c r="H42" t="n">
-        <v>3158.749495214784</v>
+        <v>0.79</v>
       </c>
       <c r="I42" t="n">
-        <v>33.21304703865982</v>
+        <v>8156.616298252074</v>
       </c>
       <c r="J42" t="n">
-        <v>58.39844729621594</v>
+        <v>7019.257724773002</v>
       </c>
       <c r="K42" t="n">
-        <v>3100.351047918567</v>
+        <v>2318.743930447655</v>
       </c>
       <c r="L42" t="n">
-        <v>32.59900962291279</v>
+        <v>1137.358573479071</v>
       </c>
       <c r="M42" t="n">
-        <v>116.7968945924319</v>
+        <v>13.94399996139088</v>
       </c>
       <c r="N42" t="n">
-        <v>3041.952600622352</v>
+        <v>5.847483854776822</v>
       </c>
       <c r="O42" t="n">
-        <v>31.98497220716576</v>
+        <v>22.04051606800495</v>
       </c>
       <c r="P42" t="n">
-        <v>175.1953418886478</v>
+        <v>31.0366450753539</v>
       </c>
       <c r="Q42" t="n">
-        <v>2983.554153326136</v>
+        <v>102.0126522650315</v>
       </c>
       <c r="R42" t="n">
-        <v>31.37093479141873</v>
+        <v>12.69332629310894</v>
       </c>
       <c r="S42" t="n">
-        <v>1622.688431693694</v>
+        <v>205.5078802710023</v>
       </c>
       <c r="T42" t="n">
-        <v>192.6271687724369</v>
+        <v>11.42447626729433</v>
       </c>
       <c r="U42" t="n">
-        <v>2966.122326442347</v>
+        <v>310.5072306670644</v>
+      </c>
+      <c r="V42" t="n">
+        <v>10.13718572233437</v>
       </c>
     </row>
     <row r="43">
@@ -3534,59 +3744,64 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F43" t="n">
-        <v>7349.075439615129</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G43" t="n">
-        <v>6351.818720757738</v>
+        <v>0.4</v>
       </c>
       <c r="H43" t="n">
-        <v>997.2567188573903</v>
+        <v>0.79</v>
       </c>
       <c r="I43" t="n">
-        <v>13.56982557944209</v>
+        <v>9156.712438756884</v>
       </c>
       <c r="J43" t="n">
-        <v>58.39844729621594</v>
+        <v>7390.293392900287</v>
       </c>
       <c r="K43" t="n">
-        <v>938.8582715611743</v>
+        <v>2634.774310847175</v>
       </c>
       <c r="L43" t="n">
-        <v>12.77518892376947</v>
+        <v>1766.419045856596</v>
       </c>
       <c r="M43" t="n">
-        <v>116.7968945924319</v>
+        <v>19.29097432807888</v>
       </c>
       <c r="N43" t="n">
-        <v>880.4598242649585</v>
+        <v>11.6855677145301</v>
       </c>
       <c r="O43" t="n">
-        <v>11.98055226809684</v>
+        <v>26.89638094162767</v>
       </c>
       <c r="P43" t="n">
-        <v>175.1953418886478</v>
+        <v>35.34683273445965</v>
       </c>
       <c r="Q43" t="n">
-        <v>822.0613769687425</v>
+        <v>107.4050077069762</v>
       </c>
       <c r="R43" t="n">
-        <v>11.18591561242422</v>
+        <v>18.11800959400717</v>
       </c>
       <c r="S43" t="n">
-        <v>512.3030311742602</v>
+        <v>216.3709596237752</v>
       </c>
       <c r="T43" t="n">
-        <v>192.6271687724369</v>
+        <v>16.92799786604695</v>
       </c>
       <c r="U43" t="n">
-        <v>804.6295500849534</v>
+        <v>326.9205413483776</v>
+      </c>
+      <c r="V43" t="n">
+        <v>15.72069139591376</v>
       </c>
     </row>
     <row r="44">
@@ -3607,59 +3822,64 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F44" t="n">
-        <v>22644.21003802981</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G44" t="n">
-        <v>13817.05108198455</v>
+        <v>0.55</v>
       </c>
       <c r="H44" t="n">
-        <v>8827.158956045258</v>
+        <v>0.79</v>
       </c>
       <c r="I44" t="n">
-        <v>38.98196908269482</v>
+        <v>17538.74293203095</v>
       </c>
       <c r="J44" t="n">
-        <v>127.0335890984213</v>
+        <v>15637.94184454893</v>
       </c>
       <c r="K44" t="n">
-        <v>8700.125366946837</v>
+        <v>7432.728462789672</v>
       </c>
       <c r="L44" t="n">
-        <v>38.42097097816799</v>
+        <v>1900.801087482025</v>
       </c>
       <c r="M44" t="n">
-        <v>254.0671781968425</v>
+        <v>10.8377270528927</v>
       </c>
       <c r="N44" t="n">
-        <v>8573.091777848414</v>
+        <v>2.60149926989962</v>
       </c>
       <c r="O44" t="n">
-        <v>37.85997287364115</v>
+        <v>20.10348330875993</v>
       </c>
       <c r="P44" t="n">
-        <v>381.1007672952638</v>
+        <v>30.39876803750127</v>
       </c>
       <c r="Q44" t="n">
-        <v>8446.058188749994</v>
+        <v>227.2701738673294</v>
       </c>
       <c r="R44" t="n">
-        <v>37.29897476911433</v>
+        <v>9.541909132828049</v>
       </c>
       <c r="S44" t="n">
-        <v>2084.604320485571</v>
+        <v>457.8433227964124</v>
       </c>
       <c r="T44" t="n">
-        <v>419.0200551550553</v>
+        <v>8.227258762373117</v>
       </c>
       <c r="U44" t="n">
-        <v>8408.138900890202</v>
+        <v>691.7674497612953</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.89350224475139</v>
       </c>
     </row>
     <row r="45">
@@ -3680,59 +3900,64 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F45" t="n">
-        <v>24908.6310418328</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G45" t="n">
-        <v>13817.05108198455</v>
+        <v>0.55</v>
       </c>
       <c r="H45" t="n">
-        <v>11091.57995984824</v>
+        <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>44.52906280244984</v>
+        <v>19650.38872319987</v>
       </c>
       <c r="J45" t="n">
-        <v>127.0335890984213</v>
+        <v>16671.59245932612</v>
       </c>
       <c r="K45" t="n">
-        <v>10964.54637074982</v>
+        <v>8350.238559052568</v>
       </c>
       <c r="L45" t="n">
-        <v>44.01906452560728</v>
+        <v>2978.796263873759</v>
       </c>
       <c r="M45" t="n">
-        <v>254.0671781968425</v>
+        <v>15.15896863840102</v>
       </c>
       <c r="N45" t="n">
-        <v>10837.5127816514</v>
+        <v>7.334984825032759</v>
       </c>
       <c r="O45" t="n">
-        <v>43.5090662487647</v>
+        <v>23.96095042844032</v>
       </c>
       <c r="P45" t="n">
-        <v>381.1007672952638</v>
+        <v>33.74093019515065</v>
       </c>
       <c r="Q45" t="n">
-        <v>10710.47919255298</v>
+        <v>242.2924803366664</v>
       </c>
       <c r="R45" t="n">
-        <v>42.99906797192213</v>
+        <v>13.92595241796051</v>
       </c>
       <c r="S45" t="n">
-        <v>2619.36548559331</v>
+        <v>488.1062587239499</v>
       </c>
       <c r="T45" t="n">
-        <v>419.0200551550553</v>
+        <v>12.67501646015389</v>
       </c>
       <c r="U45" t="n">
-        <v>10672.55990469319</v>
+        <v>737.4925110792501</v>
+      </c>
+      <c r="V45" t="n">
+        <v>11.40590033289445</v>
       </c>
     </row>
     <row r="46">
@@ -3753,59 +3978,64 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F46" t="n">
-        <v>19247.57853232534</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G46" t="n">
-        <v>13817.05108198455</v>
+        <v>0.55</v>
       </c>
       <c r="H46" t="n">
-        <v>5430.527450340784</v>
+        <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>28.2140812737586</v>
+        <v>22269.68813880771</v>
       </c>
       <c r="J46" t="n">
-        <v>127.0335890984213</v>
+        <v>17953.73952326615</v>
       </c>
       <c r="K46" t="n">
-        <v>5303.493861242362</v>
+        <v>9488.324155134174</v>
       </c>
       <c r="L46" t="n">
-        <v>27.55408350372704</v>
+        <v>4315.948615541558</v>
       </c>
       <c r="M46" t="n">
-        <v>254.0671781968425</v>
+        <v>19.38037294747958</v>
       </c>
       <c r="N46" t="n">
-        <v>5176.460272143941</v>
+        <v>11.95910868480756</v>
       </c>
       <c r="O46" t="n">
-        <v>26.89408573369548</v>
+        <v>27.72929524298561</v>
       </c>
       <c r="P46" t="n">
-        <v>381.1007672952638</v>
+        <v>37.00587557132563</v>
       </c>
       <c r="Q46" t="n">
-        <v>5049.42668304552</v>
+        <v>260.9262487086029</v>
       </c>
       <c r="R46" t="n">
-        <v>26.23408796366391</v>
+        <v>18.20870746621086</v>
       </c>
       <c r="S46" t="n">
-        <v>1282.462572823963</v>
+        <v>525.6446047482125</v>
       </c>
       <c r="T46" t="n">
-        <v>419.0200551550553</v>
+        <v>17.02001387342406</v>
       </c>
       <c r="U46" t="n">
-        <v>5011.507395185728</v>
+        <v>794.2101797761641</v>
+      </c>
+      <c r="V46" t="n">
+        <v>15.81404469525698</v>
       </c>
     </row>
     <row r="47">
@@ -3826,59 +4056,64 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F47" t="n">
-        <v>22644.21003802981</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G47" t="n">
-        <v>14750.76208031789</v>
+        <v>0.55</v>
       </c>
       <c r="H47" t="n">
-        <v>7893.447957711924</v>
+        <v>0.79</v>
       </c>
       <c r="I47" t="n">
-        <v>34.85857066532802</v>
+        <v>19289.91208758651</v>
       </c>
       <c r="J47" t="n">
-        <v>135.6181024359747</v>
+        <v>17389.11100010448</v>
       </c>
       <c r="K47" t="n">
-        <v>7757.829855275949</v>
+        <v>7432.728462789672</v>
       </c>
       <c r="L47" t="n">
-        <v>34.25966214872174</v>
+        <v>1900.801087482025</v>
       </c>
       <c r="M47" t="n">
-        <v>271.2362048719494</v>
+        <v>9.853860809999404</v>
       </c>
       <c r="N47" t="n">
-        <v>7622.211752839974</v>
+        <v>2.365330994017213</v>
       </c>
       <c r="O47" t="n">
-        <v>33.66075363211547</v>
+        <v>18.27845685297938</v>
       </c>
       <c r="P47" t="n">
-        <v>406.854307307924</v>
+        <v>27.63911912295711</v>
       </c>
       <c r="Q47" t="n">
-        <v>7486.593650404</v>
+        <v>252.7203592184756</v>
       </c>
       <c r="R47" t="n">
-        <v>33.06184511550919</v>
+        <v>8.54374411236496</v>
       </c>
       <c r="S47" t="n">
-        <v>1746.104940844108</v>
+        <v>509.1135674953733</v>
       </c>
       <c r="T47" t="n">
-        <v>447.3360562828677</v>
+        <v>7.214587156580324</v>
       </c>
       <c r="U47" t="n">
-        <v>7446.111901429056</v>
+        <v>769.233003277315</v>
+      </c>
+      <c r="V47" t="n">
+        <v>5.86611322574611</v>
       </c>
     </row>
     <row r="48">
@@ -3899,59 +4134,64 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F48" t="n">
-        <v>24908.6310418328</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G48" t="n">
-        <v>14750.76208031789</v>
+        <v>0.55</v>
       </c>
       <c r="H48" t="n">
-        <v>10157.86896151491</v>
+        <v>0.79</v>
       </c>
       <c r="I48" t="n">
-        <v>40.78051878666185</v>
+        <v>21401.55787875543</v>
       </c>
       <c r="J48" t="n">
-        <v>135.6181024359747</v>
+        <v>18422.76161488167</v>
       </c>
       <c r="K48" t="n">
-        <v>10022.25085907893</v>
+        <v>8350.238559052568</v>
       </c>
       <c r="L48" t="n">
-        <v>40.23605649883796</v>
+        <v>2978.796263873759</v>
       </c>
       <c r="M48" t="n">
-        <v>271.2362048719494</v>
+        <v>13.91859546276631</v>
       </c>
       <c r="N48" t="n">
-        <v>9886.632756642959</v>
+        <v>6.734804256177254</v>
       </c>
       <c r="O48" t="n">
-        <v>39.69159421101407</v>
+        <v>22.00036057017901</v>
       </c>
       <c r="P48" t="n">
-        <v>406.854307307924</v>
+        <v>30.98009957841534</v>
       </c>
       <c r="Q48" t="n">
-        <v>9751.014654206985</v>
+        <v>267.7426656878126</v>
       </c>
       <c r="R48" t="n">
-        <v>39.14713192319018</v>
+        <v>12.66755258446449</v>
       </c>
       <c r="S48" t="n">
-        <v>2247.016167987701</v>
+        <v>539.3765034229108</v>
       </c>
       <c r="T48" t="n">
-        <v>447.3360562828677</v>
+        <v>11.39832798280715</v>
       </c>
       <c r="U48" t="n">
-        <v>9710.532905232041</v>
+        <v>814.9580645952697</v>
+      </c>
+      <c r="V48" t="n">
+        <v>10.11065741819877</v>
       </c>
     </row>
     <row r="49">
@@ -3972,59 +4212,64 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F49" t="n">
-        <v>19247.57853232534</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G49" t="n">
-        <v>14750.76208031789</v>
+        <v>0.55</v>
       </c>
       <c r="H49" t="n">
-        <v>4496.81645200745</v>
+        <v>0.79</v>
       </c>
       <c r="I49" t="n">
-        <v>23.36302431215061</v>
+        <v>24020.85729436327</v>
       </c>
       <c r="J49" t="n">
-        <v>135.6181024359747</v>
+        <v>19704.90867882171</v>
       </c>
       <c r="K49" t="n">
-        <v>4361.198349571475</v>
+        <v>9488.324155134174</v>
       </c>
       <c r="L49" t="n">
-        <v>22.65842605731969</v>
+        <v>4315.948615541558</v>
       </c>
       <c r="M49" t="n">
-        <v>271.2362048719494</v>
+        <v>17.96750450099189</v>
       </c>
       <c r="N49" t="n">
-        <v>4225.5802471355</v>
+        <v>11.08726543624516</v>
       </c>
       <c r="O49" t="n">
-        <v>21.95382780248877</v>
+        <v>25.70777344883196</v>
       </c>
       <c r="P49" t="n">
-        <v>406.854307307924</v>
+        <v>34.30807227976538</v>
       </c>
       <c r="Q49" t="n">
-        <v>4089.962144699526</v>
+        <v>286.3764340597491</v>
       </c>
       <c r="R49" t="n">
-        <v>21.24922954765785</v>
+        <v>16.77530544435393</v>
       </c>
       <c r="S49" t="n">
-        <v>994.7381001287192</v>
+        <v>576.9148494471733</v>
       </c>
       <c r="T49" t="n">
-        <v>447.3360562828677</v>
+        <v>15.5657798565407</v>
       </c>
       <c r="U49" t="n">
-        <v>4049.480395724582</v>
+        <v>871.6757332921836</v>
+      </c>
+      <c r="V49" t="n">
+        <v>14.33867592668147</v>
       </c>
     </row>
     <row r="50">
@@ -4045,59 +4290,64 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F50" t="n">
-        <v>17703.65512064149</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G50" t="n">
-        <v>10852.71813155156</v>
+        <v>0.55</v>
       </c>
       <c r="H50" t="n">
-        <v>6850.936989089929</v>
+        <v>0.83</v>
       </c>
       <c r="I50" t="n">
-        <v>38.69786743135384</v>
+        <v>13837.32067332521</v>
       </c>
       <c r="J50" t="n">
-        <v>99.77959316674171</v>
+        <v>12915.92005202739</v>
       </c>
       <c r="K50" t="n">
-        <v>6751.157395923187</v>
+        <v>6105.272240206291</v>
       </c>
       <c r="L50" t="n">
-        <v>38.13425730402819</v>
+        <v>921.4006212978202</v>
       </c>
       <c r="M50" t="n">
-        <v>199.5591863334834</v>
+        <v>6.658808038423533</v>
       </c>
       <c r="N50" t="n">
-        <v>6651.377802756446</v>
+        <v>-0.4826785537526659</v>
       </c>
       <c r="O50" t="n">
-        <v>37.57064717670254</v>
+        <v>14.82050700091062</v>
       </c>
       <c r="P50" t="n">
-        <v>299.3387795002251</v>
+        <v>30.12369255557393</v>
       </c>
       <c r="Q50" t="n">
-        <v>6551.598209589703</v>
+        <v>187.7103409809656</v>
       </c>
       <c r="R50" t="n">
-        <v>37.00703704937688</v>
+        <v>5.302256828745905</v>
       </c>
       <c r="S50" t="n">
-        <v>2059.82108314713</v>
+        <v>378.1487239418495</v>
       </c>
       <c r="T50" t="n">
-        <v>329.1228007396091</v>
+        <v>3.925990516380967</v>
       </c>
       <c r="U50" t="n">
-        <v>6521.814188350319</v>
+        <v>571.3547962084447</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.529722576742576</v>
       </c>
     </row>
     <row r="51">
@@ -4118,59 +4368,64 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F51" t="n">
-        <v>19474.02063270564</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G51" t="n">
-        <v>10852.71813155156</v>
+        <v>0.55</v>
       </c>
       <c r="H51" t="n">
-        <v>8621.302501154081</v>
+        <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>44.27078857395805</v>
+        <v>15488.24374642091</v>
       </c>
       <c r="J51" t="n">
-        <v>99.77959316674171</v>
+        <v>13760.36720391584</v>
       </c>
       <c r="K51" t="n">
-        <v>8521.522907987339</v>
+        <v>6858.918623074479</v>
       </c>
       <c r="L51" t="n">
-        <v>43.75841573093472</v>
+        <v>1727.876542505071</v>
       </c>
       <c r="M51" t="n">
-        <v>199.5591863334834</v>
+        <v>11.15605210503196</v>
       </c>
       <c r="N51" t="n">
-        <v>8421.743314820598</v>
+        <v>4.365411693273384</v>
       </c>
       <c r="O51" t="n">
-        <v>43.24604288791141</v>
+        <v>18.91678400418463</v>
       </c>
       <c r="P51" t="n">
-        <v>299.3387795002251</v>
+        <v>33.46815631509589</v>
       </c>
       <c r="Q51" t="n">
-        <v>8321.963721653856</v>
+        <v>199.9829055511145</v>
       </c>
       <c r="R51" t="n">
-        <v>42.73367004488809</v>
+        <v>9.864860483662193</v>
       </c>
       <c r="S51" t="n">
-        <v>2592.103924521025</v>
+        <v>402.8722133747857</v>
       </c>
       <c r="T51" t="n">
-        <v>329.1228007396091</v>
+        <v>8.554903647074083</v>
       </c>
       <c r="U51" t="n">
-        <v>8292.179700414472</v>
+        <v>608.7101629521629</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7.225908875636919</v>
       </c>
     </row>
     <row r="52">
@@ -4191,59 +4446,64 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F52" t="n">
-        <v>15048.10685254526</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G52" t="n">
-        <v>10852.71813155156</v>
+        <v>0.55</v>
       </c>
       <c r="H52" t="n">
-        <v>4195.388720993704</v>
+        <v>0.83</v>
       </c>
       <c r="I52" t="n">
-        <v>27.87984403688687</v>
+        <v>17536.05965316886</v>
       </c>
       <c r="J52" t="n">
-        <v>99.77959316674171</v>
+        <v>14807.82504021741</v>
       </c>
       <c r="K52" t="n">
-        <v>4095.609127826962</v>
+        <v>7793.746584504917</v>
       </c>
       <c r="L52" t="n">
-        <v>27.21677329885668</v>
+        <v>2728.234612951444</v>
       </c>
       <c r="M52" t="n">
-        <v>199.5591863334834</v>
+        <v>15.55785431226244</v>
       </c>
       <c r="N52" t="n">
-        <v>3995.82953466022</v>
+        <v>9.110614318290224</v>
       </c>
       <c r="O52" t="n">
-        <v>26.5537025608265</v>
+        <v>22.92612859108781</v>
       </c>
       <c r="P52" t="n">
-        <v>299.3387795002251</v>
+        <v>36.7416428638854</v>
       </c>
       <c r="Q52" t="n">
-        <v>3896.049941493479</v>
+        <v>215.205875871722</v>
       </c>
       <c r="R52" t="n">
-        <v>25.89063182279633</v>
+        <v>14.33063519845865</v>
       </c>
       <c r="S52" t="n">
-        <v>1261.396821086288</v>
+        <v>433.5393933034937</v>
       </c>
       <c r="T52" t="n">
-        <v>329.1228007396091</v>
+        <v>13.08558059810938</v>
       </c>
       <c r="U52" t="n">
-        <v>3866.265920254094</v>
+        <v>655.0460071031248</v>
+      </c>
+      <c r="V52" t="n">
+        <v>11.82243130356644</v>
       </c>
     </row>
     <row r="53">
@@ -4264,59 +4524,64 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F53" t="n">
-        <v>17703.65512064149</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G53" t="n">
-        <v>11786.42912988489</v>
+        <v>0.55</v>
       </c>
       <c r="H53" t="n">
-        <v>5917.225990756595</v>
+        <v>0.83</v>
       </c>
       <c r="I53" t="n">
-        <v>33.42375317658236</v>
+        <v>15713.57333999187</v>
       </c>
       <c r="J53" t="n">
-        <v>108.3641065042951</v>
+        <v>14792.17271869405</v>
       </c>
       <c r="K53" t="n">
-        <v>5808.8618842523</v>
+        <v>6105.272240206291</v>
       </c>
       <c r="L53" t="n">
-        <v>32.81165298729462</v>
+        <v>921.4006212978202</v>
       </c>
       <c r="M53" t="n">
-        <v>216.7282130085903</v>
+        <v>5.863724318852459</v>
       </c>
       <c r="N53" t="n">
-        <v>5700.497777748004</v>
+        <v>-0.425045136831743</v>
       </c>
       <c r="O53" t="n">
-        <v>32.19955279800688</v>
+        <v>13.05088941106298</v>
       </c>
       <c r="P53" t="n">
-        <v>325.0923195128854</v>
+        <v>26.52682395895772</v>
       </c>
       <c r="Q53" t="n">
-        <v>5592.13367124371</v>
+        <v>214.9783967143366</v>
       </c>
       <c r="R53" t="n">
-        <v>31.58745260871914</v>
+        <v>4.495617955882777</v>
       </c>
       <c r="S53" t="n">
-        <v>1638.15109494454</v>
+        <v>433.0811289764505</v>
       </c>
       <c r="T53" t="n">
-        <v>357.4388018674215</v>
+        <v>3.107628556253152</v>
       </c>
       <c r="U53" t="n">
-        <v>5559.787188889173</v>
+        <v>654.3536035470371</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.699467154750437</v>
       </c>
     </row>
     <row r="54">
@@ -4337,59 +4602,64 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F54" t="n">
-        <v>19474.02063270564</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G54" t="n">
-        <v>11786.42912988489</v>
+        <v>0.55</v>
       </c>
       <c r="H54" t="n">
-        <v>7687.591502820747</v>
+        <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>39.47613925143852</v>
+        <v>17364.49641308757</v>
       </c>
       <c r="J54" t="n">
-        <v>108.3641065042951</v>
+        <v>15636.6198705825</v>
       </c>
       <c r="K54" t="n">
-        <v>7579.227396316453</v>
+        <v>6858.918623074479</v>
       </c>
       <c r="L54" t="n">
-        <v>38.91968453390422</v>
+        <v>1727.87654250507</v>
       </c>
       <c r="M54" t="n">
-        <v>216.7282130085903</v>
+        <v>9.950628577991894</v>
       </c>
       <c r="N54" t="n">
-        <v>7470.863289812157</v>
+        <v>3.89372422617073</v>
       </c>
       <c r="O54" t="n">
-        <v>38.3632298163699</v>
+        <v>16.87280498007322</v>
       </c>
       <c r="P54" t="n">
-        <v>325.0923195128854</v>
+        <v>29.8518857339757</v>
       </c>
       <c r="Q54" t="n">
-        <v>7362.499183307862</v>
+        <v>227.2509612844854</v>
       </c>
       <c r="R54" t="n">
-        <v>37.80677509883559</v>
+        <v>8.641918230865404</v>
       </c>
       <c r="S54" t="n">
-        <v>2128.266937498177</v>
+        <v>457.8046184093866</v>
       </c>
       <c r="T54" t="n">
-        <v>357.4388018674215</v>
+        <v>7.314188064437234</v>
       </c>
       <c r="U54" t="n">
-        <v>7330.152700953326</v>
+        <v>691.7089702907554</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5.967161658850974</v>
       </c>
     </row>
     <row r="55">
@@ -4410,59 +4680,64 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F55" t="n">
-        <v>15048.10685254526</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G55" t="n">
-        <v>11786.42912988489</v>
+        <v>0.55</v>
       </c>
       <c r="H55" t="n">
-        <v>3261.67772266037</v>
+        <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>21.67500373715571</v>
+        <v>19412.31231983552</v>
       </c>
       <c r="J55" t="n">
-        <v>108.3641065042951</v>
+        <v>16684.07770688408</v>
       </c>
       <c r="K55" t="n">
-        <v>3153.313616156075</v>
+        <v>7793.746584504917</v>
       </c>
       <c r="L55" t="n">
-        <v>20.95488586740543</v>
+        <v>2728.234612951444</v>
       </c>
       <c r="M55" t="n">
-        <v>216.7282130085903</v>
+        <v>14.05414547222039</v>
       </c>
       <c r="N55" t="n">
-        <v>3044.949509651779</v>
+        <v>8.230048720126163</v>
       </c>
       <c r="O55" t="n">
-        <v>20.23476799765514</v>
+        <v>20.71025604604234</v>
       </c>
       <c r="P55" t="n">
-        <v>325.0923195128854</v>
+        <v>33.19046337195852</v>
       </c>
       <c r="Q55" t="n">
-        <v>2936.585403147485</v>
+        <v>242.473931605093</v>
       </c>
       <c r="R55" t="n">
-        <v>19.51465012790486</v>
+        <v>12.80507257657501</v>
       </c>
       <c r="S55" t="n">
-        <v>902.9773311140871</v>
+        <v>488.4717983380947</v>
       </c>
       <c r="T55" t="n">
-        <v>357.4388018674215</v>
+        <v>11.53784658783156</v>
       </c>
       <c r="U55" t="n">
-        <v>2904.238920792948</v>
+        <v>738.0448144417173</v>
+      </c>
+      <c r="V55" t="n">
+        <v>10.25220368248531</v>
       </c>
     </row>
     <row r="56">
@@ -4483,59 +4758,64 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F56" t="n">
-        <v>11527.96147390608</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G56" t="n">
-        <v>7147.301943510316</v>
+        <v>0.3</v>
       </c>
       <c r="H56" t="n">
-        <v>4380.659530395767</v>
+        <v>0.87</v>
       </c>
       <c r="I56" t="n">
-        <v>38.00029641243626</v>
+        <v>17391.50998883192</v>
       </c>
       <c r="J56" t="n">
-        <v>65.71209825214224</v>
+        <v>17393.04372205156</v>
       </c>
       <c r="K56" t="n">
-        <v>4314.947432143626</v>
+        <v>2272.97330708513</v>
       </c>
       <c r="L56" t="n">
-        <v>37.43027283627421</v>
+        <v>-1.53373321964682</v>
       </c>
       <c r="M56" t="n">
-        <v>131.4241965042845</v>
+        <v>-0.008818861735592352</v>
       </c>
       <c r="N56" t="n">
-        <v>4249.235333891483</v>
+        <v>-3.272902463824368</v>
       </c>
       <c r="O56" t="n">
-        <v>36.86024926011216</v>
+        <v>3.799278674034607</v>
       </c>
       <c r="P56" t="n">
-        <v>197.1362947564267</v>
+        <v>14.67955734766378</v>
       </c>
       <c r="Q56" t="n">
-        <v>4183.523235639341</v>
+        <v>252.7775144636843</v>
       </c>
       <c r="R56" t="n">
-        <v>36.29022568395012</v>
+        <v>-1.462272383747236</v>
       </c>
       <c r="S56" t="n">
-        <v>1999.932880055138</v>
+        <v>509.2287086374612</v>
       </c>
       <c r="T56" t="n">
-        <v>216.7512327203015</v>
+        <v>-2.93684931432117</v>
       </c>
       <c r="U56" t="n">
-        <v>4163.908297675466</v>
+        <v>769.4069730400239</v>
+      </c>
+      <c r="V56" t="n">
+        <v>-4.4328566453099</v>
       </c>
     </row>
     <row r="57">
@@ -4556,59 +4836,64 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F57" t="n">
-        <v>12680.75762129669</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G57" t="n">
-        <v>7147.301943510316</v>
+        <v>0.3</v>
       </c>
       <c r="H57" t="n">
-        <v>5533.455677786378</v>
+        <v>0.87</v>
       </c>
       <c r="I57" t="n">
-        <v>43.63663310221479</v>
+        <v>18466.52966433609</v>
       </c>
       <c r="J57" t="n">
-        <v>65.71209825214224</v>
+        <v>17732.74993951089</v>
       </c>
       <c r="K57" t="n">
-        <v>5467.743579534236</v>
+        <v>2553.553442391721</v>
       </c>
       <c r="L57" t="n">
-        <v>43.11842985115839</v>
+        <v>733.7797248252064</v>
       </c>
       <c r="M57" t="n">
-        <v>131.4241965042845</v>
+        <v>3.973565895504098</v>
       </c>
       <c r="N57" t="n">
-        <v>5402.031481282093</v>
+        <v>0.7947131791008119</v>
       </c>
       <c r="O57" t="n">
-        <v>42.60022660010198</v>
+        <v>7.682227397974592</v>
       </c>
       <c r="P57" t="n">
-        <v>197.1362947564267</v>
+        <v>18.27840311931887</v>
       </c>
       <c r="Q57" t="n">
-        <v>5336.319383029951</v>
+        <v>257.7145510554085</v>
       </c>
       <c r="R57" t="n">
-        <v>42.08202334904558</v>
+        <v>2.577989380913349</v>
       </c>
       <c r="S57" t="n">
-        <v>2526.226901119834</v>
+        <v>519.1745330254955</v>
       </c>
       <c r="T57" t="n">
-        <v>216.7512327203015</v>
+        <v>1.16213059898402</v>
       </c>
       <c r="U57" t="n">
-        <v>5316.704445066077</v>
+        <v>784.434379207403</v>
+      </c>
+      <c r="V57" t="n">
+        <v>-0.2743052176177131</v>
       </c>
     </row>
     <row r="58">
@@ -4629,59 +4914,64 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F58" t="n">
-        <v>9798.767252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G58" t="n">
-        <v>7147.301943510316</v>
+        <v>0.3</v>
       </c>
       <c r="H58" t="n">
-        <v>2651.465309309855</v>
+        <v>0.87</v>
       </c>
       <c r="I58" t="n">
-        <v>27.05917224992501</v>
+        <v>19799.99118500917</v>
       </c>
       <c r="J58" t="n">
-        <v>65.71209825214224</v>
+        <v>18154.12378004358</v>
       </c>
       <c r="K58" t="n">
-        <v>2585.753211057713</v>
+        <v>2901.586899287395</v>
       </c>
       <c r="L58" t="n">
-        <v>26.38855627796966</v>
+        <v>1645.867404965593</v>
       </c>
       <c r="M58" t="n">
-        <v>131.4241965042845</v>
+        <v>8.312465341962879</v>
       </c>
       <c r="N58" t="n">
-        <v>2520.041112805571</v>
+        <v>5.226473628517578</v>
       </c>
       <c r="O58" t="n">
-        <v>25.71794030601432</v>
+        <v>11.91278900764904</v>
       </c>
       <c r="P58" t="n">
-        <v>197.1362947564267</v>
+        <v>22.19942805246669</v>
       </c>
       <c r="Q58" t="n">
-        <v>2454.329014553428</v>
+        <v>263.8384839202945</v>
       </c>
       <c r="R58" t="n">
-        <v>25.04732433405897</v>
+        <v>6.979947153166664</v>
       </c>
       <c r="S58" t="n">
-        <v>1210.491848458096</v>
+        <v>531.511399424332</v>
       </c>
       <c r="T58" t="n">
-        <v>216.7512327203015</v>
+        <v>5.628063139669244</v>
       </c>
       <c r="U58" t="n">
-        <v>2434.714076589554</v>
+        <v>803.0744732785441</v>
+      </c>
+      <c r="V58" t="n">
+        <v>4.256531853030006</v>
       </c>
     </row>
     <row r="59">
@@ -4702,59 +4992,64 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F59" t="n">
-        <v>11527.96147390608</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G59" t="n">
-        <v>8081.01294184365</v>
+        <v>0.3</v>
       </c>
       <c r="H59" t="n">
-        <v>3446.948532062434</v>
+        <v>0.87</v>
       </c>
       <c r="I59" t="n">
-        <v>29.90076380689434</v>
+        <v>17391.50998883192</v>
       </c>
       <c r="J59" t="n">
-        <v>74.29661158969567</v>
+        <v>17393.04372205156</v>
       </c>
       <c r="K59" t="n">
-        <v>3372.651920472738</v>
+        <v>2272.97330708513</v>
       </c>
       <c r="L59" t="n">
-        <v>29.25627334986195</v>
+        <v>-1.53373321964682</v>
       </c>
       <c r="M59" t="n">
-        <v>148.5932231793913</v>
+        <v>-0.008818861735592352</v>
       </c>
       <c r="N59" t="n">
-        <v>3298.355308883042</v>
+        <v>-3.272902463824368</v>
       </c>
       <c r="O59" t="n">
-        <v>28.61178289282955</v>
+        <v>3.799278674034607</v>
       </c>
       <c r="P59" t="n">
-        <v>222.889834769087</v>
+        <v>14.67955734766378</v>
       </c>
       <c r="Q59" t="n">
-        <v>3224.058697293347</v>
+        <v>252.7775144636843</v>
       </c>
       <c r="R59" t="n">
-        <v>27.96729243579716</v>
+        <v>-1.462272383747236</v>
       </c>
       <c r="S59" t="n">
-        <v>1391.832733004676</v>
+        <v>509.2287086374612</v>
       </c>
       <c r="T59" t="n">
-        <v>245.0672338481138</v>
+        <v>-2.93684931432117</v>
       </c>
       <c r="U59" t="n">
-        <v>3201.88129821432</v>
+        <v>769.4069730400239</v>
+      </c>
+      <c r="V59" t="n">
+        <v>-4.4328566453099</v>
       </c>
     </row>
     <row r="60">
@@ -4775,59 +5070,64 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F60" t="n">
-        <v>12680.75762129669</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G60" t="n">
-        <v>8081.01294184365</v>
+        <v>0.3</v>
       </c>
       <c r="H60" t="n">
-        <v>4599.744679453044</v>
+        <v>0.87</v>
       </c>
       <c r="I60" t="n">
-        <v>36.27342164263123</v>
+        <v>18466.52966433609</v>
       </c>
       <c r="J60" t="n">
-        <v>74.29661158969567</v>
+        <v>17732.74993951089</v>
       </c>
       <c r="K60" t="n">
-        <v>4525.448067863348</v>
+        <v>2553.553442391721</v>
       </c>
       <c r="L60" t="n">
-        <v>35.68752122714724</v>
+        <v>733.7797248252064</v>
       </c>
       <c r="M60" t="n">
-        <v>148.5932231793913</v>
+        <v>3.973565895504098</v>
       </c>
       <c r="N60" t="n">
-        <v>4451.151456273653</v>
+        <v>0.7947131791008119</v>
       </c>
       <c r="O60" t="n">
-        <v>35.10162081166325</v>
+        <v>7.682227397974592</v>
       </c>
       <c r="P60" t="n">
-        <v>222.889834769087</v>
+        <v>18.27840311931887</v>
       </c>
       <c r="Q60" t="n">
-        <v>4376.854844683957</v>
+        <v>257.7145510554085</v>
       </c>
       <c r="R60" t="n">
-        <v>34.51572039617925</v>
+        <v>2.577989380913349</v>
       </c>
       <c r="S60" t="n">
-        <v>1857.316739364325</v>
+        <v>519.1745330254955</v>
       </c>
       <c r="T60" t="n">
-        <v>245.0672338481138</v>
+        <v>1.16213059898402</v>
       </c>
       <c r="U60" t="n">
-        <v>4354.677445604931</v>
+        <v>784.434379207403</v>
+      </c>
+      <c r="V60" t="n">
+        <v>-0.2743052176177131</v>
       </c>
     </row>
     <row r="61">
@@ -4848,59 +5148,64 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F61" t="n">
-        <v>9798.767252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G61" t="n">
-        <v>8081.01294184365</v>
+        <v>0.3</v>
       </c>
       <c r="H61" t="n">
-        <v>1717.754310976521</v>
+        <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>17.53031036105217</v>
+        <v>19799.99118500917</v>
       </c>
       <c r="J61" t="n">
-        <v>74.29661158969567</v>
+        <v>18154.12378004358</v>
       </c>
       <c r="K61" t="n">
-        <v>1643.457699386825</v>
+        <v>2901.586899287395</v>
       </c>
       <c r="L61" t="n">
-        <v>16.77208629395523</v>
+        <v>1645.867404965593</v>
       </c>
       <c r="M61" t="n">
-        <v>148.5932231793913</v>
+        <v>8.312465341962879</v>
       </c>
       <c r="N61" t="n">
-        <v>1569.16108779713</v>
+        <v>5.226473628517578</v>
       </c>
       <c r="O61" t="n">
-        <v>16.0138622268583</v>
+        <v>11.91278900764904</v>
       </c>
       <c r="P61" t="n">
-        <v>222.889834769087</v>
+        <v>22.19942805246669</v>
       </c>
       <c r="Q61" t="n">
-        <v>1494.864476207434</v>
+        <v>263.8384839202945</v>
       </c>
       <c r="R61" t="n">
-        <v>15.25563815976136</v>
+        <v>6.979947153166664</v>
       </c>
       <c r="S61" t="n">
-        <v>693.6067234652029</v>
+        <v>531.511399424332</v>
       </c>
       <c r="T61" t="n">
-        <v>245.0672338481138</v>
+        <v>5.628063139669244</v>
       </c>
       <c r="U61" t="n">
-        <v>1472.687077128407</v>
+        <v>803.0744732785441</v>
+      </c>
+      <c r="V61" t="n">
+        <v>4.256531853030006</v>
       </c>
     </row>
   </sheetData>
